--- a/data_room/hollis_voice/02_financials/financial_model.xlsx
+++ b/data_room/hollis_voice/02_financials/financial_model.xlsx
@@ -14,12 +14,14 @@
     <sheet name="Cohorts" sheetId="5" r:id="rId5"/>
     <sheet name="Hiring_Plan" sheetId="6" r:id="rId6"/>
     <sheet name="Cash_Runway" sheetId="7" r:id="rId7"/>
+    <sheet name="Cash_Bridge" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ARR_TOTAL">ARR_Build!$E$15</definedName>
     <definedName name="AS_OF_DATE">Assumptions!$B$5</definedName>
     <definedName name="AVG_BASE_NOW">Assumptions!$B$10</definedName>
     <definedName name="AVG_NET_BURN_12M">Cash_Runway!$B$4</definedName>
+    <definedName name="CASH_BRIDGE_DIFF">Cash_Bridge!$B$12</definedName>
     <definedName name="CASH_START">Assumptions!$B$6</definedName>
     <definedName name="COHORT_CUSTOMERS">Cohorts!$B$14</definedName>
     <definedName name="GM_PCT">'P&amp;L'!$W$17</definedName>
@@ -27,9 +29,12 @@
     <definedName name="HOSTING_USD_MONTH">Assumptions!$B$13</definedName>
     <definedName name="LICENCES_PCT">Assumptions!$B$12</definedName>
     <definedName name="LOAD_FACTOR">Assumptions!$B$8</definedName>
+    <definedName name="NET_LOSS_BEFORE_2025_USD">Assumptions!$B$21</definedName>
     <definedName name="NRR_12M">Cohorts!$E$14</definedName>
-    <definedName name="PAYROLL_NOW_USD_MONTH">Assumptions!$B$19</definedName>
+    <definedName name="PAYROLL_NOW_USD_MONTH">Assumptions!$B$22</definedName>
     <definedName name="PROGRAMS_USD_MONTH">Assumptions!$B$15</definedName>
+    <definedName name="RAISED_PRESEED_SAFE_USD">Assumptions!$B$19</definedName>
+    <definedName name="RAISED_SEED_SAFE_USD">Assumptions!$B$20</definedName>
     <definedName name="RENT_ETC_USD_MONTH">Assumptions!$B$14</definedName>
     <definedName name="REV_GROWTH">Assumptions!$B$7</definedName>
     <definedName name="REV_START_USD_MONTH">Assumptions!$B$18</definedName>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="269">
   <si>
     <t>Hollis Voice: financial model</t>
   </si>
@@ -73,6 +78,9 @@
     <t>Cash_Runway: monthly cash and the number of months the cash lasts.</t>
   </si>
   <si>
+    <t>Cash_Bridge: money raised, less losses since the company began, equals cash at the data date.</t>
+  </si>
+  <si>
     <t>Definitions</t>
   </si>
   <si>
@@ -190,6 +198,24 @@
     <t>From P&amp;L, 2026-09.</t>
   </si>
   <si>
+    <t>Raised in 2024: pre-seed SAFEs (USD)</t>
+  </si>
+  <si>
+    <t>Two SAFEs on a $12,000,000 post-money cap. See the cap table.</t>
+  </si>
+  <si>
+    <t>Raised in 2025: seed SAFE (USD)</t>
+  </si>
+  <si>
+    <t>One SAFE on a $28,000,000 post-money cap. See the cap table.</t>
+  </si>
+  <si>
+    <t>Net loss before 2025-01 (USD)</t>
+  </si>
+  <si>
+    <t>Spend in 2024 before the first paying clinic. Cash_Bridge ties this to cash.</t>
+  </si>
+  <si>
     <t>Payroll today (USD a month)</t>
   </si>
   <si>
@@ -460,13 +486,13 @@
     <t>Six-month pilot signed 2026-08-01. Counted at $15,000 a month times 12.</t>
   </si>
   <si>
-    <t>Onboarding fees (one-time, excluded)</t>
+    <t>Onboarding fees</t>
   </si>
   <si>
     <t>Onboarding</t>
   </si>
   <si>
-    <t>$500 per new clinic. September 2026: 19 new clinics, $9,500 in fees. One-time, so not counted in ARR.</t>
+    <t>$500 per new clinic. September 2026: 19 new clinics, $9,500 in fees.</t>
   </si>
   <si>
     <t>ARR total</t>
@@ -743,15 +769,103 @@
   </si>
   <si>
     <t>2030-09</t>
+  </si>
+  <si>
+    <t>2030-10</t>
+  </si>
+  <si>
+    <t>2030-11</t>
+  </si>
+  <si>
+    <t>2030-12</t>
+  </si>
+  <si>
+    <t>2031-01</t>
+  </si>
+  <si>
+    <t>2031-02</t>
+  </si>
+  <si>
+    <t>2031-03</t>
+  </si>
+  <si>
+    <t>2031-04</t>
+  </si>
+  <si>
+    <t>2031-05</t>
+  </si>
+  <si>
+    <t>2031-06</t>
+  </si>
+  <si>
+    <t>2031-07</t>
+  </si>
+  <si>
+    <t>2031-08</t>
+  </si>
+  <si>
+    <t>2031-09</t>
+  </si>
+  <si>
+    <t>Cash bridge: money raised to cash at the data date (USD)</t>
+  </si>
+  <si>
+    <t>Cash burn is taken as the operating result in the P&amp;L. The model does not track working capital timing.</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Raised in 2024: pre-seed SAFEs</t>
+  </si>
+  <si>
+    <t>Two SAFEs. See the cap table.</t>
+  </si>
+  <si>
+    <t>Raised in 2025: seed SAFE</t>
+  </si>
+  <si>
+    <t>One SAFE. See the cap table.</t>
+  </si>
+  <si>
+    <t>Total raised before the Series A</t>
+  </si>
+  <si>
+    <t>Less: net loss before 2025-01</t>
+  </si>
+  <si>
+    <t>2024 spend, before the first paying clinic.</t>
+  </si>
+  <si>
+    <t>Less: net loss 2025-01 to 2026-09</t>
+  </si>
+  <si>
+    <t>Sum of the P&amp;L operating result over the 21 actual months.</t>
+  </si>
+  <si>
+    <t>Cash at 2026-09-30 from the bridge</t>
+  </si>
+  <si>
+    <t>Cash at 2026-09-30 in Assumptions</t>
+  </si>
+  <si>
+    <t>Bank balance.</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Rounding only: the loss before 2025 is stated in whole dollars.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -841,7 +955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -857,6 +971,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1151,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -1202,13 +1317,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1227,9 +1342,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.7109375" customWidth="1"/>
@@ -1249,194 +1369,227 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="6">
         <v>1800000</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="7">
         <v>0.035</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6">
         <v>1.28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6">
         <v>140000</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="7">
         <v>0.15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="7">
         <v>0.05</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="6">
         <v>20541.29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="6">
         <v>60000</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="6">
         <v>140000</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6">
         <v>9000000</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6">
         <v>4</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="6">
         <v>186739</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6">
+        <v>3500000</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="6">
+        <v>592499</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="6">
         <f>STAFF_NOW*AVG_BASE_NOW*LOAD_FACTOR/12</f>
         <v>253866.66666666666</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>14</v>
+      <c r="C22" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1456,227 +1609,227 @@
   <sheetData>
     <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:35">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:35">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:35">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:35">
       <c r="A6" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1715,70 +1868,70 @@
     </row>
     <row r="7" spans="1:35">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C7" s="10">
-        <v>2645</v>
+        <v>2651</v>
       </c>
       <c r="D7" s="10">
-        <v>6790</v>
+        <v>6828</v>
       </c>
       <c r="E7" s="10">
-        <v>9934</v>
+        <v>10024</v>
       </c>
       <c r="F7" s="10">
-        <v>12279</v>
+        <v>12366</v>
       </c>
       <c r="G7" s="10">
-        <v>16072</v>
+        <v>16059</v>
       </c>
       <c r="H7" s="10">
-        <v>19516</v>
+        <v>19462</v>
       </c>
       <c r="I7" s="10">
-        <v>23110</v>
+        <v>23092</v>
       </c>
       <c r="J7" s="10">
-        <v>28651</v>
+        <v>28610</v>
       </c>
       <c r="K7" s="10">
-        <v>34642</v>
+        <v>34539</v>
       </c>
       <c r="L7" s="10">
-        <v>40682</v>
+        <v>40585</v>
       </c>
       <c r="M7" s="10">
-        <v>65971</v>
+        <v>65867</v>
       </c>
       <c r="N7" s="10">
-        <v>72859</v>
+        <v>72656</v>
       </c>
       <c r="O7" s="10">
-        <v>77249</v>
+        <v>77134</v>
       </c>
       <c r="P7" s="10">
-        <v>85735</v>
+        <v>85778</v>
       </c>
       <c r="Q7" s="10">
-        <v>95975</v>
+        <v>95824</v>
       </c>
       <c r="R7" s="10">
-        <v>122963</v>
+        <v>122664</v>
       </c>
       <c r="S7" s="10">
-        <v>133950</v>
+        <v>133652</v>
       </c>
       <c r="T7" s="10">
-        <v>142837</v>
+        <v>142497</v>
       </c>
       <c r="U7" s="10">
-        <v>150175</v>
+        <v>149831</v>
       </c>
       <c r="V7" s="10">
-        <v>161257</v>
+        <v>160971</v>
       </c>
       <c r="W7" s="10">
         <v>171739</v>
@@ -1786,10 +1939,10 @@
     </row>
     <row r="8" spans="1:35">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -1857,10 +2010,10 @@
     </row>
     <row r="9" spans="1:35">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C9" s="10">
         <v>2500</v>
@@ -1964,90 +2117,90 @@
     </row>
     <row r="10" spans="1:35">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C10" s="10">
         <f>C7+C8</f>
-        <v>2645</v>
+        <v>2651</v>
       </c>
       <c r="D10" s="10">
         <f>D7+D8</f>
-        <v>6790</v>
+        <v>6828</v>
       </c>
       <c r="E10" s="10">
         <f>E7+E8</f>
-        <v>9934</v>
+        <v>10024</v>
       </c>
       <c r="F10" s="10">
         <f>F7+F8</f>
-        <v>12279</v>
+        <v>12366</v>
       </c>
       <c r="G10" s="10">
         <f>G7+G8</f>
-        <v>16072</v>
+        <v>16059</v>
       </c>
       <c r="H10" s="10">
         <f>H7+H8</f>
-        <v>19516</v>
+        <v>19462</v>
       </c>
       <c r="I10" s="10">
         <f>I7+I8</f>
-        <v>23110</v>
+        <v>23092</v>
       </c>
       <c r="J10" s="10">
         <f>J7+J8</f>
-        <v>28651</v>
+        <v>28610</v>
       </c>
       <c r="K10" s="10">
         <f>K7+K8</f>
-        <v>34642</v>
+        <v>34539</v>
       </c>
       <c r="L10" s="10">
         <f>L7+L8</f>
-        <v>40682</v>
+        <v>40585</v>
       </c>
       <c r="M10" s="10">
         <f>M7+M8</f>
-        <v>65971</v>
+        <v>65867</v>
       </c>
       <c r="N10" s="10">
         <f>N7+N8</f>
-        <v>72859</v>
+        <v>72656</v>
       </c>
       <c r="O10" s="10">
         <f>O7+O8</f>
-        <v>77249</v>
+        <v>77134</v>
       </c>
       <c r="P10" s="10">
         <f>P7+P8</f>
-        <v>85735</v>
+        <v>85778</v>
       </c>
       <c r="Q10" s="10">
         <f>Q7+Q8</f>
-        <v>95975</v>
+        <v>95824</v>
       </c>
       <c r="R10" s="10">
         <f>R7+R8</f>
-        <v>122963</v>
+        <v>122664</v>
       </c>
       <c r="S10" s="10">
         <f>S7+S8</f>
-        <v>133950</v>
+        <v>133652</v>
       </c>
       <c r="T10" s="10">
         <f>T7+T8</f>
-        <v>142837</v>
+        <v>142497</v>
       </c>
       <c r="U10" s="10">
         <f>U7+U8</f>
-        <v>150175</v>
+        <v>149831</v>
       </c>
       <c r="V10" s="10">
         <f>V7+V8</f>
-        <v>176257</v>
+        <v>175971</v>
       </c>
       <c r="W10" s="10">
         <f>W7+W8</f>
@@ -2092,90 +2245,90 @@
     </row>
     <row r="11" spans="1:35">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C11" s="10">
         <f>C10+C9</f>
-        <v>5145</v>
+        <v>5151</v>
       </c>
       <c r="D11" s="10">
         <f>D10+D9</f>
-        <v>9790</v>
+        <v>9828</v>
       </c>
       <c r="E11" s="10">
         <f>E10+E9</f>
-        <v>12934</v>
+        <v>13024</v>
       </c>
       <c r="F11" s="10">
         <f>F10+F9</f>
-        <v>15779</v>
+        <v>15866</v>
       </c>
       <c r="G11" s="10">
         <f>G10+G9</f>
-        <v>19572</v>
+        <v>19559</v>
       </c>
       <c r="H11" s="10">
         <f>H10+H9</f>
-        <v>23016</v>
+        <v>22962</v>
       </c>
       <c r="I11" s="10">
         <f>I10+I9</f>
-        <v>27610</v>
+        <v>27592</v>
       </c>
       <c r="J11" s="10">
         <f>J10+J9</f>
-        <v>33651</v>
+        <v>33610</v>
       </c>
       <c r="K11" s="10">
         <f>K10+K9</f>
-        <v>40142</v>
+        <v>40039</v>
       </c>
       <c r="L11" s="10">
         <f>L10+L9</f>
-        <v>47182</v>
+        <v>47085</v>
       </c>
       <c r="M11" s="10">
         <f>M10+M9</f>
-        <v>72971</v>
+        <v>72867</v>
       </c>
       <c r="N11" s="10">
         <f>N10+N9</f>
-        <v>79359</v>
+        <v>79156</v>
       </c>
       <c r="O11" s="10">
         <f>O10+O9</f>
-        <v>83249</v>
+        <v>83134</v>
       </c>
       <c r="P11" s="10">
         <f>P10+P9</f>
-        <v>93235</v>
+        <v>93278</v>
       </c>
       <c r="Q11" s="10">
         <f>Q10+Q9</f>
-        <v>102975</v>
+        <v>102824</v>
       </c>
       <c r="R11" s="10">
         <f>R10+R9</f>
-        <v>129963</v>
+        <v>129664</v>
       </c>
       <c r="S11" s="10">
         <f>S10+S9</f>
-        <v>141450</v>
+        <v>141152</v>
       </c>
       <c r="T11" s="10">
         <f>T10+T9</f>
-        <v>150837</v>
+        <v>150497</v>
       </c>
       <c r="U11" s="10">
         <f>U10+U9</f>
-        <v>159175</v>
+        <v>158831</v>
       </c>
       <c r="V11" s="10">
         <f>V10+V9</f>
-        <v>185757</v>
+        <v>185471</v>
       </c>
       <c r="W11" s="10">
         <f>W10+W9</f>
@@ -2232,7 +2385,7 @@
     </row>
     <row r="12" spans="1:35">
       <c r="A12" s="9" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2271,73 +2424,73 @@
     </row>
     <row r="13" spans="1:35">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C13" s="10">
-        <v>396.75</v>
+        <v>435.7</v>
       </c>
       <c r="D13" s="10">
-        <v>1018.5</v>
+        <v>1136.51</v>
       </c>
       <c r="E13" s="10">
-        <v>1490.1</v>
+        <v>1635.42</v>
       </c>
       <c r="F13" s="10">
-        <v>1841.85</v>
+        <v>1921.19</v>
       </c>
       <c r="G13" s="10">
-        <v>2410.8</v>
+        <v>2597.46</v>
       </c>
       <c r="H13" s="10">
-        <v>2927.4</v>
+        <v>3146.04</v>
       </c>
       <c r="I13" s="10">
-        <v>3466.5</v>
+        <v>3815.97</v>
       </c>
       <c r="J13" s="10">
-        <v>4297.65</v>
+        <v>4513.24</v>
       </c>
       <c r="K13" s="10">
-        <v>5196.3</v>
+        <v>5442.28</v>
       </c>
       <c r="L13" s="10">
-        <v>6102.3</v>
+        <v>6522.2</v>
       </c>
       <c r="M13" s="10">
-        <v>9895.65</v>
+        <v>10085.63</v>
       </c>
       <c r="N13" s="10">
-        <v>10928.85</v>
+        <v>11562.23</v>
       </c>
       <c r="O13" s="10">
-        <v>11587.35</v>
+        <v>11550.18</v>
       </c>
       <c r="P13" s="10">
-        <v>12860.25</v>
+        <v>13419.25</v>
       </c>
       <c r="Q13" s="10">
-        <v>14396.25</v>
+        <v>14895.05</v>
       </c>
       <c r="R13" s="10">
-        <v>18444.45</v>
+        <v>18999.36</v>
       </c>
       <c r="S13" s="10">
-        <v>20092.5</v>
+        <v>20335.17</v>
       </c>
       <c r="T13" s="10">
-        <v>21425.55</v>
+        <v>22105.48</v>
       </c>
       <c r="U13" s="10">
-        <v>22526.25</v>
+        <v>22876.86</v>
       </c>
       <c r="V13" s="10">
-        <v>26438.55</v>
+        <v>25950.57</v>
       </c>
       <c r="W13" s="10">
-        <v>28010.85</v>
+        <v>28298.55</v>
       </c>
       <c r="X13" s="10">
         <v>28991.22975</v>
@@ -2378,73 +2531,73 @@
     </row>
     <row r="14" spans="1:35">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C14" s="10">
-        <v>132.25</v>
+        <v>148.48</v>
       </c>
       <c r="D14" s="10">
-        <v>339.5</v>
+        <v>385.03</v>
       </c>
       <c r="E14" s="10">
-        <v>496.7</v>
+        <v>648.38</v>
       </c>
       <c r="F14" s="10">
-        <v>613.95</v>
+        <v>701.91</v>
       </c>
       <c r="G14" s="10">
-        <v>803.6</v>
+        <v>939.74</v>
       </c>
       <c r="H14" s="10">
-        <v>975.8</v>
+        <v>1140.98</v>
       </c>
       <c r="I14" s="10">
-        <v>1155.5</v>
+        <v>1312.02</v>
       </c>
       <c r="J14" s="10">
-        <v>1432.55</v>
+        <v>1637.24</v>
       </c>
       <c r="K14" s="10">
-        <v>1732.1</v>
+        <v>1813.47</v>
       </c>
       <c r="L14" s="10">
-        <v>2034.1</v>
+        <v>2216.35</v>
       </c>
       <c r="M14" s="10">
-        <v>3298.55</v>
+        <v>3157.99</v>
       </c>
       <c r="N14" s="10">
-        <v>3642.95</v>
+        <v>3843.81</v>
       </c>
       <c r="O14" s="10">
-        <v>3862.45</v>
+        <v>3935.01</v>
       </c>
       <c r="P14" s="10">
-        <v>4286.75</v>
+        <v>5224.99</v>
       </c>
       <c r="Q14" s="10">
-        <v>4798.75</v>
+        <v>5048.01</v>
       </c>
       <c r="R14" s="10">
-        <v>6148.15</v>
+        <v>6532.87</v>
       </c>
       <c r="S14" s="10">
-        <v>6697.5</v>
+        <v>6877.81</v>
       </c>
       <c r="T14" s="10">
-        <v>7141.85</v>
+        <v>7126.35</v>
       </c>
       <c r="U14" s="10">
-        <v>7508.75</v>
+        <v>7054.51</v>
       </c>
       <c r="V14" s="10">
-        <v>8812.85</v>
+        <v>8891.51</v>
       </c>
       <c r="W14" s="10">
-        <v>9336.950000000001</v>
+        <v>9049.25</v>
       </c>
       <c r="X14" s="10">
         <v>9663.74325</v>
@@ -2485,90 +2638,90 @@
     </row>
     <row r="15" spans="1:35">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C15" s="10">
         <f>C13+C14</f>
-        <v>529.0</v>
+        <v>584.18</v>
       </c>
       <c r="D15" s="10">
         <f>D13+D14</f>
-        <v>1358.0</v>
+        <v>1521.54</v>
       </c>
       <c r="E15" s="10">
         <f>E13+E14</f>
-        <v>1986.8</v>
+        <v>2283.8</v>
       </c>
       <c r="F15" s="10">
         <f>F13+F14</f>
-        <v>2455.8</v>
+        <v>2623.1</v>
       </c>
       <c r="G15" s="10">
         <f>G13+G14</f>
-        <v>3214.4</v>
+        <v>3537.2</v>
       </c>
       <c r="H15" s="10">
         <f>H13+H14</f>
-        <v>3903.2</v>
+        <v>4287.02</v>
       </c>
       <c r="I15" s="10">
         <f>I13+I14</f>
-        <v>4622.0</v>
+        <v>5127.99</v>
       </c>
       <c r="J15" s="10">
         <f>J13+J14</f>
-        <v>5730.2</v>
+        <v>6150.48</v>
       </c>
       <c r="K15" s="10">
         <f>K13+K14</f>
-        <v>6928.4</v>
+        <v>7255.75</v>
       </c>
       <c r="L15" s="10">
         <f>L13+L14</f>
-        <v>8136.4</v>
+        <v>8738.55</v>
       </c>
       <c r="M15" s="10">
         <f>M13+M14</f>
-        <v>13194.2</v>
+        <v>13243.619999999999</v>
       </c>
       <c r="N15" s="10">
         <f>N13+N14</f>
-        <v>14571.8</v>
+        <v>15406.039999999999</v>
       </c>
       <c r="O15" s="10">
         <f>O13+O14</f>
-        <v>15449.8</v>
+        <v>15485.19</v>
       </c>
       <c r="P15" s="10">
         <f>P13+P14</f>
-        <v>17147.0</v>
+        <v>18644.239999999998</v>
       </c>
       <c r="Q15" s="10">
         <f>Q13+Q14</f>
-        <v>19195.0</v>
+        <v>19943.059999999998</v>
       </c>
       <c r="R15" s="10">
         <f>R13+R14</f>
-        <v>24592.6</v>
+        <v>25532.23</v>
       </c>
       <c r="S15" s="10">
         <f>S13+S14</f>
-        <v>26790.0</v>
+        <v>27212.98</v>
       </c>
       <c r="T15" s="10">
         <f>T13+T14</f>
-        <v>28567.4</v>
+        <v>29231.83</v>
       </c>
       <c r="U15" s="10">
         <f>U13+U14</f>
-        <v>30035.0</v>
+        <v>29931.370000000003</v>
       </c>
       <c r="V15" s="10">
         <f>V13+V14</f>
-        <v>35251.4</v>
+        <v>34842.08</v>
       </c>
       <c r="W15" s="10">
         <f>W13+W14</f>
@@ -2625,87 +2778,87 @@
     </row>
     <row r="16" spans="1:35">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C16" s="11">
         <f>C10-C15</f>
-        <v>2116.0</v>
+        <v>2066.82</v>
       </c>
       <c r="D16" s="11">
         <f>D10-D15</f>
-        <v>5432.0</v>
+        <v>5306.46</v>
       </c>
       <c r="E16" s="11">
         <f>E10-E15</f>
-        <v>7947.2</v>
+        <v>7740.2</v>
       </c>
       <c r="F16" s="11">
         <f>F10-F15</f>
-        <v>9823.2</v>
+        <v>9742.9</v>
       </c>
       <c r="G16" s="11">
         <f>G10-G15</f>
-        <v>12857.6</v>
+        <v>12521.8</v>
       </c>
       <c r="H16" s="11">
         <f>H10-H15</f>
-        <v>15612.8</v>
+        <v>15174.98</v>
       </c>
       <c r="I16" s="11">
         <f>I10-I15</f>
-        <v>18488.0</v>
+        <v>17964.010000000002</v>
       </c>
       <c r="J16" s="11">
         <f>J10-J15</f>
-        <v>22920.8</v>
+        <v>22459.52</v>
       </c>
       <c r="K16" s="11">
         <f>K10-K15</f>
-        <v>27713.6</v>
+        <v>27283.25</v>
       </c>
       <c r="L16" s="11">
         <f>L10-L15</f>
-        <v>32545.6</v>
+        <v>31846.45</v>
       </c>
       <c r="M16" s="11">
         <f>M10-M15</f>
-        <v>52776.8</v>
+        <v>52623.380000000005</v>
       </c>
       <c r="N16" s="11">
         <f>N10-N15</f>
-        <v>58287.2</v>
+        <v>57249.96</v>
       </c>
       <c r="O16" s="11">
         <f>O10-O15</f>
-        <v>61799.2</v>
+        <v>61648.81</v>
       </c>
       <c r="P16" s="11">
         <f>P10-P15</f>
-        <v>68588.0</v>
+        <v>67133.76000000001</v>
       </c>
       <c r="Q16" s="11">
         <f>Q10-Q15</f>
-        <v>76780.0</v>
+        <v>75880.94</v>
       </c>
       <c r="R16" s="11">
         <f>R10-R15</f>
-        <v>98370.4</v>
+        <v>97131.77</v>
       </c>
       <c r="S16" s="11">
         <f>S10-S15</f>
-        <v>107160.0</v>
+        <v>106439.02</v>
       </c>
       <c r="T16" s="11">
         <f>T10-T15</f>
-        <v>114269.6</v>
+        <v>113265.17</v>
       </c>
       <c r="U16" s="11">
         <f>U10-U15</f>
-        <v>120140.0</v>
+        <v>119899.63</v>
       </c>
       <c r="V16" s="11">
         <f>V10-V15</f>
-        <v>141005.6</v>
+        <v>141128.91999999998</v>
       </c>
       <c r="W16" s="11">
         <f>W10-W15</f>
@@ -2762,87 +2915,87 @@
     </row>
     <row r="17" spans="1:35">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C17" s="12">
         <f>C16/C10</f>
-        <v>0.8</v>
+        <v>0.7796378725009431</v>
       </c>
       <c r="D17" s="12">
         <f>D16/D10</f>
-        <v>0.8</v>
+        <v>0.7771616871704745</v>
       </c>
       <c r="E17" s="12">
         <f>E16/E10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7721667996807662</v>
       </c>
       <c r="F17" s="12">
         <f>F16/F10</f>
-        <v>0.8</v>
+        <v>0.7878780527252143</v>
       </c>
       <c r="G17" s="12">
         <f>G16/G10</f>
-        <v>0.8</v>
+        <v>0.7797372190049193</v>
       </c>
       <c r="H17" s="12">
         <f>H16/H10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7797235638680505</v>
       </c>
       <c r="I17" s="12">
         <f>I16/I10</f>
-        <v>0.8</v>
+        <v>0.7779321843062533</v>
       </c>
       <c r="J17" s="12">
         <f>J16/J10</f>
-        <v>0.7999999999999999</v>
+        <v>0.78502341838518</v>
       </c>
       <c r="K17" s="12">
         <f>K16/K10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7899258808882712</v>
       </c>
       <c r="L17" s="12">
         <f>L16/L10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7846852285327092</v>
       </c>
       <c r="M17" s="12">
         <f>M16/M10</f>
-        <v>0.8</v>
+        <v>0.798933912277772</v>
       </c>
       <c r="N17" s="12">
         <f>N16/N10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7879591499669676</v>
       </c>
       <c r="O17" s="12">
         <f>O16/O10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7992430056784298</v>
       </c>
       <c r="P17" s="12">
         <f>P16/P10</f>
-        <v>0.8</v>
+        <v>0.7826454335610531</v>
       </c>
       <c r="Q17" s="12">
         <f>Q16/Q10</f>
-        <v>0.8</v>
+        <v>0.7918782350976791</v>
       </c>
       <c r="R17" s="12">
         <f>R16/R10</f>
-        <v>0.7999999999999999</v>
+        <v>0.7918522957020805</v>
       </c>
       <c r="S17" s="12">
         <f>S16/S10</f>
-        <v>0.8</v>
+        <v>0.7963892796217041</v>
       </c>
       <c r="T17" s="12">
         <f>T16/T10</f>
-        <v>0.8</v>
+        <v>0.7948600321410275</v>
       </c>
       <c r="U17" s="12">
         <f>U16/U10</f>
-        <v>0.8</v>
+        <v>0.800232461907082</v>
       </c>
       <c r="V17" s="12">
         <f>V16/V10</f>
-        <v>0.8</v>
+        <v>0.8020010115303089</v>
       </c>
       <c r="W17" s="12">
         <f>W16/W10</f>
@@ -2899,7 +3052,7 @@
     </row>
     <row r="18" spans="1:35">
       <c r="A18" s="9" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2938,177 +3091,177 @@
     </row>
     <row r="19" spans="1:35">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C19" s="10">
-        <v>27231.37</v>
+        <v>31186.59</v>
       </c>
       <c r="D19" s="10">
-        <v>34039.22</v>
+        <v>46627.52</v>
       </c>
       <c r="E19" s="10">
-        <v>34039.22</v>
+        <v>46538.95</v>
       </c>
       <c r="F19" s="10">
-        <v>40847.06</v>
+        <v>47695.48</v>
       </c>
       <c r="G19" s="10">
-        <v>47654.9</v>
+        <v>65151.44</v>
       </c>
       <c r="H19" s="10">
-        <v>47654.9</v>
+        <v>64853.75</v>
       </c>
       <c r="I19" s="10">
-        <v>54462.75</v>
+        <v>63121.10000000001</v>
       </c>
       <c r="J19" s="10">
-        <v>61270.59</v>
+        <v>62974.97</v>
       </c>
       <c r="K19" s="10">
-        <v>61270.59</v>
+        <v>63289.46</v>
       </c>
       <c r="L19" s="10">
-        <v>68078.42999999999</v>
+        <v>78382.33</v>
       </c>
       <c r="M19" s="10">
-        <v>68078.42999999999</v>
+        <v>81073.95999999999</v>
       </c>
       <c r="N19" s="10">
-        <v>74886.27</v>
+        <v>81059.22</v>
       </c>
       <c r="O19" s="10">
-        <v>81694.12</v>
+        <v>99412.06</v>
       </c>
       <c r="P19" s="10">
-        <v>81694.12</v>
+        <v>99699.81</v>
       </c>
       <c r="Q19" s="10">
-        <v>88501.96000000001</v>
+        <v>96893.14999999999</v>
       </c>
       <c r="R19" s="10">
-        <v>95309.8</v>
+        <v>99024.84</v>
       </c>
       <c r="S19" s="10">
-        <v>95309.8</v>
+        <v>98478.56</v>
       </c>
       <c r="T19" s="10">
-        <v>102117.65</v>
+        <v>115147.66</v>
       </c>
       <c r="U19" s="10">
-        <v>108925.49</v>
+        <v>113937.76</v>
       </c>
       <c r="V19" s="10">
-        <v>108925.49</v>
+        <v>115946.68</v>
       </c>
       <c r="W19" s="10">
         <v>115733.33</v>
       </c>
       <c r="X19" s="10">
-        <v>136000</v>
+        <v>136106.6666666667</v>
       </c>
       <c r="Y19" s="10">
-        <v>155733.3333333333</v>
+        <v>156266.6666666667</v>
       </c>
       <c r="Z19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AA19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AB19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AC19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AD19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AE19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AF19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AG19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AH19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
       <c r="AI19" s="10">
-        <v>174400</v>
+        <v>174773.3333333333</v>
       </c>
     </row>
     <row r="20" spans="1:35">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C20" s="10">
-        <v>290.95</v>
+        <v>384.59</v>
       </c>
       <c r="D20" s="10">
-        <v>746.9</v>
+        <v>889.04</v>
       </c>
       <c r="E20" s="10">
-        <v>1092.74</v>
+        <v>1471.02</v>
       </c>
       <c r="F20" s="10">
-        <v>1350.69</v>
+        <v>1673.15</v>
       </c>
       <c r="G20" s="10">
-        <v>1767.92</v>
+        <v>1989.73</v>
       </c>
       <c r="H20" s="10">
-        <v>2146.76</v>
+        <v>2387.55</v>
       </c>
       <c r="I20" s="10">
-        <v>2542.1</v>
+        <v>2969.36</v>
       </c>
       <c r="J20" s="10">
-        <v>3151.61</v>
+        <v>3587.41</v>
       </c>
       <c r="K20" s="10">
-        <v>3810.62</v>
+        <v>4351.33</v>
       </c>
       <c r="L20" s="10">
-        <v>4475.02</v>
+        <v>5283.21</v>
       </c>
       <c r="M20" s="10">
-        <v>7256.81</v>
+        <v>8135.71</v>
       </c>
       <c r="N20" s="10">
-        <v>8014.49</v>
+        <v>9216.5</v>
       </c>
       <c r="O20" s="10">
-        <v>8497.389999999999</v>
+        <v>9565.969999999999</v>
       </c>
       <c r="P20" s="10">
-        <v>9430.85</v>
+        <v>10374.25</v>
       </c>
       <c r="Q20" s="10">
-        <v>10557.25</v>
+        <v>11323.71</v>
       </c>
       <c r="R20" s="10">
-        <v>13525.93</v>
+        <v>13828.95</v>
       </c>
       <c r="S20" s="10">
-        <v>14734.5</v>
+        <v>14870.87</v>
       </c>
       <c r="T20" s="10">
-        <v>15712.07</v>
+        <v>16089.51</v>
       </c>
       <c r="U20" s="10">
-        <v>16519.25</v>
+        <v>17347.66</v>
       </c>
       <c r="V20" s="10">
-        <v>19388.27</v>
+        <v>19734.17</v>
       </c>
       <c r="W20" s="10">
         <v>20541.29</v>
@@ -3152,177 +3305,177 @@
     </row>
     <row r="21" spans="1:35">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C21" s="10">
-        <v>20329.41</v>
+        <v>14987.33</v>
       </c>
       <c r="D21" s="10">
-        <v>25411.76</v>
+        <v>14512.14</v>
       </c>
       <c r="E21" s="10">
-        <v>25411.76</v>
+        <v>15141.47</v>
       </c>
       <c r="F21" s="10">
-        <v>30494.12</v>
+        <v>29802.29</v>
       </c>
       <c r="G21" s="10">
-        <v>35576.47</v>
+        <v>28981</v>
       </c>
       <c r="H21" s="10">
-        <v>35576.47</v>
+        <v>29027.22</v>
       </c>
       <c r="I21" s="10">
-        <v>40658.82</v>
+        <v>29807.41</v>
       </c>
       <c r="J21" s="10">
-        <v>45741.18</v>
+        <v>42768.19</v>
       </c>
       <c r="K21" s="10">
-        <v>45741.18</v>
+        <v>43425.31</v>
       </c>
       <c r="L21" s="10">
-        <v>50823.53</v>
+        <v>44478.8</v>
       </c>
       <c r="M21" s="10">
-        <v>50823.53</v>
+        <v>43524.61</v>
       </c>
       <c r="N21" s="10">
-        <v>55905.88</v>
+        <v>57574.62</v>
       </c>
       <c r="O21" s="10">
-        <v>60988.24</v>
+        <v>60851.2</v>
       </c>
       <c r="P21" s="10">
-        <v>60988.24</v>
+        <v>60043.2</v>
       </c>
       <c r="Q21" s="10">
-        <v>66070.59</v>
+        <v>59932.4</v>
       </c>
       <c r="R21" s="10">
-        <v>71152.94</v>
+        <v>74155.14</v>
       </c>
       <c r="S21" s="10">
-        <v>71152.94</v>
+        <v>72970.5</v>
       </c>
       <c r="T21" s="10">
-        <v>76235.28999999999</v>
+        <v>72738</v>
       </c>
       <c r="U21" s="10">
-        <v>81317.64999999999</v>
+        <v>73276.44</v>
       </c>
       <c r="V21" s="10">
-        <v>81317.64999999999</v>
+        <v>73020.25</v>
       </c>
       <c r="W21" s="10">
         <v>86400</v>
       </c>
       <c r="X21" s="10">
-        <v>101333.3333333333</v>
+        <v>101226.6666666667</v>
       </c>
       <c r="Y21" s="10">
-        <v>116800</v>
+        <v>116266.6666666667</v>
       </c>
       <c r="Z21" s="10">
-        <v>133333.3333333333</v>
+        <v>132960</v>
       </c>
       <c r="AA21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AB21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AC21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AD21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AE21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AF21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AG21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AH21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
       <c r="AI21" s="10">
-        <v>156266.6666666667</v>
+        <v>155466.6666666667</v>
       </c>
     </row>
     <row r="22" spans="1:35">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C22" s="10">
-        <v>4768.63</v>
+        <v>0</v>
       </c>
       <c r="D22" s="10">
-        <v>5960.78</v>
+        <v>0</v>
       </c>
       <c r="E22" s="10">
-        <v>5960.78</v>
+        <v>0</v>
       </c>
       <c r="F22" s="10">
-        <v>7152.94</v>
+        <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>8345.1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10">
-        <v>8345.1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="10">
-        <v>9537.25</v>
+        <v>9692.92</v>
       </c>
       <c r="J22" s="10">
-        <v>10729.41</v>
+        <v>9821.189999999999</v>
       </c>
       <c r="K22" s="10">
-        <v>10729.41</v>
+        <v>9568.060000000001</v>
       </c>
       <c r="L22" s="10">
-        <v>11921.57</v>
+        <v>9594.24</v>
       </c>
       <c r="M22" s="10">
-        <v>11921.57</v>
+        <v>9830.01</v>
       </c>
       <c r="N22" s="10">
-        <v>13113.73</v>
+        <v>9581.09</v>
       </c>
       <c r="O22" s="10">
-        <v>14305.88</v>
+        <v>10023.15</v>
       </c>
       <c r="P22" s="10">
-        <v>14305.88</v>
+        <v>10078.63</v>
       </c>
       <c r="Q22" s="10">
-        <v>15498.04</v>
+        <v>20475.78</v>
       </c>
       <c r="R22" s="10">
-        <v>16690.2</v>
+        <v>20085.22</v>
       </c>
       <c r="S22" s="10">
-        <v>16690.2</v>
+        <v>20326.91</v>
       </c>
       <c r="T22" s="10">
-        <v>17882.35</v>
+        <v>20211.2</v>
       </c>
       <c r="U22" s="10">
-        <v>19074.51</v>
+        <v>20754.39</v>
       </c>
       <c r="V22" s="10">
-        <v>19074.51</v>
+        <v>20137</v>
       </c>
       <c r="W22" s="10">
         <v>20266.67</v>
@@ -3337,39 +3490,39 @@
         <v>20266.66666666667</v>
       </c>
       <c r="AA22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AB22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AC22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AD22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AE22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AF22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AG22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AH22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
       <c r="AI22" s="10">
-        <v>32533.33333333334</v>
+        <v>32960</v>
       </c>
     </row>
     <row r="23" spans="1:35">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -3473,70 +3626,70 @@
     </row>
     <row r="24" spans="1:35">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C24" s="10">
-        <v>7403.92</v>
+        <v>15663.86</v>
       </c>
       <c r="D24" s="10">
-        <v>9254.9</v>
+        <v>15644.32</v>
       </c>
       <c r="E24" s="10">
-        <v>9254.9</v>
+        <v>15674.88</v>
       </c>
       <c r="F24" s="10">
-        <v>11105.88</v>
+        <v>15543.54</v>
       </c>
       <c r="G24" s="10">
-        <v>12956.86</v>
+        <v>15324.49</v>
       </c>
       <c r="H24" s="10">
-        <v>12956.86</v>
+        <v>15281.11</v>
       </c>
       <c r="I24" s="10">
-        <v>14807.84</v>
+        <v>15477.72</v>
       </c>
       <c r="J24" s="10">
-        <v>16658.82</v>
+        <v>15578.31</v>
       </c>
       <c r="K24" s="10">
-        <v>16658.82</v>
+        <v>15587.4</v>
       </c>
       <c r="L24" s="10">
-        <v>18509.8</v>
+        <v>15737.25</v>
       </c>
       <c r="M24" s="10">
-        <v>18509.8</v>
+        <v>15379.03</v>
       </c>
       <c r="N24" s="10">
-        <v>20360.78</v>
+        <v>15392.87</v>
       </c>
       <c r="O24" s="10">
-        <v>22211.76</v>
+        <v>16070.23</v>
       </c>
       <c r="P24" s="10">
-        <v>22211.76</v>
+        <v>15995.43</v>
       </c>
       <c r="Q24" s="10">
-        <v>24062.75</v>
+        <v>15832.97</v>
       </c>
       <c r="R24" s="10">
-        <v>25913.73</v>
+        <v>16170.87</v>
       </c>
       <c r="S24" s="10">
-        <v>25913.73</v>
+        <v>16607.25</v>
       </c>
       <c r="T24" s="10">
-        <v>27764.71</v>
+        <v>16299.85</v>
       </c>
       <c r="U24" s="10">
-        <v>29615.69</v>
+        <v>31079.66</v>
       </c>
       <c r="V24" s="10">
-        <v>29615.69</v>
+        <v>31111.67</v>
       </c>
       <c r="W24" s="10">
         <v>31466.67</v>
@@ -3580,73 +3733,73 @@
     </row>
     <row r="25" spans="1:35">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C25" s="10">
-        <v>32470.59</v>
+        <v>29694.61</v>
       </c>
       <c r="D25" s="10">
-        <v>34588.24</v>
+        <v>29278.84</v>
       </c>
       <c r="E25" s="10">
-        <v>34588.24</v>
+        <v>38685.46</v>
       </c>
       <c r="F25" s="10">
-        <v>36705.88</v>
+        <v>29916.65</v>
       </c>
       <c r="G25" s="10">
-        <v>38823.53</v>
+        <v>33015.32</v>
       </c>
       <c r="H25" s="10">
-        <v>38823.53</v>
+        <v>31875.77</v>
       </c>
       <c r="I25" s="10">
-        <v>40941.18</v>
+        <v>42747.61</v>
       </c>
       <c r="J25" s="10">
-        <v>43058.82</v>
+        <v>40478.87</v>
       </c>
       <c r="K25" s="10">
-        <v>43058.82</v>
+        <v>40198.46</v>
       </c>
       <c r="L25" s="10">
-        <v>45176.47</v>
+        <v>37320.55</v>
       </c>
       <c r="M25" s="10">
-        <v>45176.47</v>
+        <v>57792.54</v>
       </c>
       <c r="N25" s="10">
-        <v>47294.12</v>
+        <v>41441.78</v>
       </c>
       <c r="O25" s="10">
-        <v>49411.76</v>
+        <v>45058.86</v>
       </c>
       <c r="P25" s="10">
-        <v>49411.76</v>
+        <v>52242.38</v>
       </c>
       <c r="Q25" s="10">
-        <v>51529.41</v>
+        <v>47510.24</v>
       </c>
       <c r="R25" s="10">
-        <v>53647.06</v>
+        <v>70654.34</v>
       </c>
       <c r="S25" s="10">
-        <v>53647.06</v>
+        <v>51638.27</v>
       </c>
       <c r="T25" s="10">
-        <v>55764.71</v>
+        <v>50592.12</v>
       </c>
       <c r="U25" s="10">
-        <v>57882.35</v>
+        <v>55773.69</v>
       </c>
       <c r="V25" s="10">
-        <v>57882.35</v>
+        <v>52293.41</v>
       </c>
       <c r="W25" s="10">
-        <v>60000</v>
+        <v>61163.46</v>
       </c>
       <c r="X25" s="10">
         <v>60000</v>
@@ -3687,91 +3840,91 @@
     </row>
     <row r="26" spans="1:35">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C26" s="11">
         <f>C19+C20+C21+C22+C23+C24+C25</f>
-        <v>92494.87</v>
+        <v>91916.98</v>
       </c>
       <c r="D26" s="11">
         <f>D19+D20+D21+D22+D23+D24+D25</f>
-        <v>110001.8</v>
+        <v>106951.86</v>
       </c>
       <c r="E26" s="11">
         <f>E19+E20+E21+E22+E23+E24+E25</f>
-        <v>110347.64</v>
+        <v>117511.78</v>
       </c>
       <c r="F26" s="11">
         <f>F19+F20+F21+F22+F23+F24+F25</f>
-        <v>127656.56999999999</v>
+        <v>124631.11</v>
       </c>
       <c r="G26" s="11">
         <f>G19+G20+G21+G22+G23+G24+G25</f>
-        <v>145124.78</v>
+        <v>144461.98</v>
       </c>
       <c r="H26" s="11">
         <f>H19+H20+H21+H22+H23+H24+H25</f>
-        <v>145503.62</v>
+        <v>143425.4</v>
       </c>
       <c r="I26" s="11">
         <f>I19+I20+I21+I22+I23+I24+I25</f>
-        <v>162949.94</v>
+        <v>163816.12</v>
       </c>
       <c r="J26" s="11">
         <f>J19+J20+J21+J22+J23+J24+J25</f>
-        <v>180610.43</v>
+        <v>175208.94</v>
       </c>
       <c r="K26" s="11">
         <f>K19+K20+K21+K22+K23+K24+K25</f>
-        <v>181269.44</v>
+        <v>176420.02</v>
       </c>
       <c r="L26" s="11">
         <f>L19+L20+L21+L22+L23+L24+L25</f>
-        <v>198984.82</v>
+        <v>190796.38</v>
       </c>
       <c r="M26" s="11">
         <f>M19+M20+M21+M22+M23+M24+M25</f>
-        <v>201766.61</v>
+        <v>215735.86</v>
       </c>
       <c r="N26" s="11">
         <f>N19+N20+N21+N22+N23+N24+N25</f>
-        <v>219575.27</v>
+        <v>214266.08</v>
       </c>
       <c r="O26" s="11">
         <f>O19+O20+O21+O22+O23+O24+O25</f>
-        <v>237109.15</v>
+        <v>240981.47</v>
       </c>
       <c r="P26" s="11">
         <f>P19+P20+P21+P22+P23+P24+P25</f>
-        <v>238042.61</v>
+        <v>248433.69999999998</v>
       </c>
       <c r="Q26" s="11">
         <f>Q19+Q20+Q21+Q22+Q23+Q24+Q25</f>
-        <v>256220.0</v>
+        <v>251968.25</v>
       </c>
       <c r="R26" s="11">
         <f>R19+R20+R21+R22+R23+R24+R25</f>
-        <v>276239.66000000003</v>
+        <v>293919.36</v>
       </c>
       <c r="S26" s="11">
         <f>S19+S20+S21+S22+S23+S24+S25</f>
-        <v>277448.23</v>
+        <v>274892.36</v>
       </c>
       <c r="T26" s="11">
         <f>T19+T20+T21+T22+T23+T24+T25</f>
-        <v>295476.77999999997</v>
+        <v>291078.34</v>
       </c>
       <c r="U26" s="11">
         <f>U19+U20+U21+U22+U23+U24+U25</f>
-        <v>313334.94</v>
+        <v>312169.60000000003</v>
       </c>
       <c r="V26" s="11">
         <f>V19+V20+V21+V22+V23+V24+V25</f>
-        <v>316203.96</v>
+        <v>312243.18</v>
       </c>
       <c r="W26" s="11">
         <f>W19+W20+W21+W22+W23+W24+W25</f>
-        <v>334407.96</v>
+        <v>335571.42</v>
       </c>
       <c r="X26" s="11">
         <f>X19+X20+X21+X22+X23+X24+X25</f>
@@ -3824,91 +3977,91 @@
     </row>
     <row r="27" spans="1:35">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C27" s="11">
         <f>C16+C9-C26</f>
-        <v>-87878.87</v>
+        <v>-87350.16</v>
       </c>
       <c r="D27" s="11">
         <f>D16+D9-D26</f>
-        <v>-101569.8</v>
+        <v>-98645.4</v>
       </c>
       <c r="E27" s="11">
         <f>E16+E9-E26</f>
-        <v>-99400.44</v>
+        <v>-106771.58</v>
       </c>
       <c r="F27" s="11">
         <f>F16+F9-F26</f>
-        <v>-114333.37</v>
+        <v>-111388.21</v>
       </c>
       <c r="G27" s="11">
         <f>G16+G9-G26</f>
-        <v>-128767.18</v>
+        <v>-128440.18000000001</v>
       </c>
       <c r="H27" s="11">
         <f>H16+H9-H26</f>
-        <v>-126390.81999999999</v>
+        <v>-124750.42</v>
       </c>
       <c r="I27" s="11">
         <f>I16+I9-I26</f>
-        <v>-139961.94</v>
+        <v>-141352.11</v>
       </c>
       <c r="J27" s="11">
         <f>J16+J9-J26</f>
-        <v>-152689.63</v>
+        <v>-147749.42</v>
       </c>
       <c r="K27" s="11">
         <f>K16+K9-K26</f>
-        <v>-148055.84</v>
+        <v>-143636.77</v>
       </c>
       <c r="L27" s="11">
         <f>L16+L9-L26</f>
-        <v>-159939.22</v>
+        <v>-152449.93</v>
       </c>
       <c r="M27" s="11">
         <f>M16+M9-M26</f>
-        <v>-141989.81</v>
+        <v>-156112.47999999998</v>
       </c>
       <c r="N27" s="11">
         <f>N16+N9-N26</f>
-        <v>-154788.07</v>
+        <v>-150516.12</v>
       </c>
       <c r="O27" s="11">
         <f>O16+O9-O26</f>
-        <v>-169309.95</v>
+        <v>-173332.66</v>
       </c>
       <c r="P27" s="11">
         <f>P16+P9-P26</f>
-        <v>-161954.61</v>
+        <v>-173799.93999999997</v>
       </c>
       <c r="Q27" s="11">
         <f>Q16+Q9-Q26</f>
-        <v>-172440.0</v>
+        <v>-169087.31</v>
       </c>
       <c r="R27" s="11">
         <f>R16+R9-R26</f>
-        <v>-170869.26000000004</v>
+        <v>-189787.58999999997</v>
       </c>
       <c r="S27" s="11">
         <f>S16+S9-S26</f>
-        <v>-162788.22999999998</v>
+        <v>-160953.33999999997</v>
       </c>
       <c r="T27" s="11">
         <f>T16+T9-T26</f>
-        <v>-173207.17999999996</v>
+        <v>-169813.17000000004</v>
       </c>
       <c r="U27" s="11">
         <f>U16+U9-U26</f>
-        <v>-184194.94</v>
+        <v>-183269.97000000003</v>
       </c>
       <c r="V27" s="11">
         <f>V16+V9-V26</f>
-        <v>-165698.36000000002</v>
+        <v>-161614.26</v>
       </c>
       <c r="W27" s="11">
         <f>W16+W9-W26</f>
-        <v>-175516.76</v>
+        <v>-176680.21999999997</v>
       </c>
       <c r="X27" s="11">
         <f>X16+X9-X26</f>
@@ -3961,7 +4114,7 @@
     </row>
     <row r="28" spans="1:35">
       <c r="A28" s="9" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4000,90 +4153,90 @@
     </row>
     <row r="29" spans="1:35">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C29" s="10">
         <f>C19+C21+C22+C24</f>
-        <v>59733.329999999994</v>
+        <v>61837.78</v>
       </c>
       <c r="D29" s="10">
         <f>D19+D21+D22+D24</f>
-        <v>74666.65999999999</v>
+        <v>76783.98000000001</v>
       </c>
       <c r="E29" s="10">
         <f>E19+E21+E22+E24</f>
-        <v>74666.65999999999</v>
+        <v>77355.3</v>
       </c>
       <c r="F29" s="10">
         <f>F19+F21+F22+F24</f>
-        <v>89600.0</v>
+        <v>93041.31</v>
       </c>
       <c r="G29" s="10">
         <f>G19+G21+G22+G24</f>
-        <v>104533.33</v>
+        <v>109456.93000000001</v>
       </c>
       <c r="H29" s="10">
         <f>H19+H21+H22+H24</f>
-        <v>104533.33</v>
+        <v>109162.08</v>
       </c>
       <c r="I29" s="10">
         <f>I19+I21+I22+I24</f>
-        <v>119466.66</v>
+        <v>118099.15000000001</v>
       </c>
       <c r="J29" s="10">
         <f>J19+J21+J22+J24</f>
-        <v>134400.0</v>
+        <v>131142.66</v>
       </c>
       <c r="K29" s="10">
         <f>K19+K21+K22+K24</f>
-        <v>134400.0</v>
+        <v>131870.22999999998</v>
       </c>
       <c r="L29" s="10">
         <f>L19+L21+L22+L24</f>
-        <v>149333.33</v>
+        <v>148192.62</v>
       </c>
       <c r="M29" s="10">
         <f>M19+M21+M22+M24</f>
-        <v>149333.33</v>
+        <v>149807.61</v>
       </c>
       <c r="N29" s="10">
         <f>N19+N21+N22+N24</f>
-        <v>164266.66</v>
+        <v>163607.8</v>
       </c>
       <c r="O29" s="10">
         <f>O19+O21+O22+O24</f>
-        <v>179200.0</v>
+        <v>186356.64</v>
       </c>
       <c r="P29" s="10">
         <f>P19+P21+P22+P24</f>
-        <v>179200.0</v>
+        <v>185817.07</v>
       </c>
       <c r="Q29" s="10">
         <f>Q19+Q21+Q22+Q24</f>
-        <v>194133.34</v>
+        <v>193134.3</v>
       </c>
       <c r="R29" s="10">
         <f>R19+R21+R22+R24</f>
-        <v>209066.67</v>
+        <v>209436.06999999998</v>
       </c>
       <c r="S29" s="10">
         <f>S19+S21+S22+S24</f>
-        <v>209066.67</v>
+        <v>208383.22</v>
       </c>
       <c r="T29" s="10">
         <f>T19+T21+T22+T24</f>
-        <v>224000.0</v>
+        <v>224396.71000000002</v>
       </c>
       <c r="U29" s="10">
         <f>U19+U21+U22+U24</f>
-        <v>238933.34000000003</v>
+        <v>239048.25000000003</v>
       </c>
       <c r="V29" s="10">
         <f>V19+V21+V22+V24</f>
-        <v>238933.34000000003</v>
+        <v>240215.59999999998</v>
       </c>
       <c r="W29" s="10">
         <f>W19+W21+W22+W24</f>
@@ -4095,11 +4248,11 @@
       </c>
       <c r="Y29" s="10">
         <f>Y19+Y21+Y22+Y24</f>
-        <v>324266.66666666674</v>
+        <v>324266.6666666667</v>
       </c>
       <c r="Z29" s="10">
         <f>Z19+Z21+Z22+Z24</f>
-        <v>359466.66666666674</v>
+        <v>359466.6666666667</v>
       </c>
       <c r="AA29" s="10">
         <f>AA19+AA21+AA22+AA24</f>
@@ -4140,94 +4293,94 @@
     </row>
     <row r="30" spans="1:35">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C30" s="10">
         <f>-C27</f>
-        <v>87878.87</v>
+        <v>87350.16</v>
       </c>
       <c r="D30" s="10">
         <f>-D27</f>
-        <v>101569.8</v>
+        <v>98645.4</v>
       </c>
       <c r="E30" s="10">
         <f>-E27</f>
-        <v>99400.44</v>
+        <v>106771.58</v>
       </c>
       <c r="F30" s="10">
         <f>-F27</f>
-        <v>114333.37</v>
+        <v>111388.21</v>
       </c>
       <c r="G30" s="10">
         <f>-G27</f>
-        <v>128767.18</v>
+        <v>128440.18000000001</v>
       </c>
       <c r="H30" s="10">
         <f>-H27</f>
-        <v>126390.81999999999</v>
+        <v>124750.42</v>
       </c>
       <c r="I30" s="10">
         <f>-I27</f>
-        <v>139961.94</v>
+        <v>141352.11</v>
       </c>
       <c r="J30" s="10">
         <f>-J27</f>
-        <v>152689.63</v>
+        <v>147749.42</v>
       </c>
       <c r="K30" s="10">
         <f>-K27</f>
-        <v>148055.84</v>
+        <v>143636.77</v>
       </c>
       <c r="L30" s="10">
         <f>-L27</f>
-        <v>159939.22</v>
+        <v>152449.93</v>
       </c>
       <c r="M30" s="10">
         <f>-M27</f>
-        <v>141989.81</v>
+        <v>156112.47999999998</v>
       </c>
       <c r="N30" s="10">
         <f>-N27</f>
-        <v>154788.07</v>
+        <v>150516.12</v>
       </c>
       <c r="O30" s="10">
         <f>-O27</f>
-        <v>169309.95</v>
+        <v>173332.66</v>
       </c>
       <c r="P30" s="10">
         <f>-P27</f>
-        <v>161954.61</v>
+        <v>173799.93999999997</v>
       </c>
       <c r="Q30" s="10">
         <f>-Q27</f>
-        <v>172440.0</v>
+        <v>169087.31</v>
       </c>
       <c r="R30" s="10">
         <f>-R27</f>
-        <v>170869.26000000004</v>
+        <v>189787.58999999997</v>
       </c>
       <c r="S30" s="10">
         <f>-S27</f>
-        <v>162788.22999999998</v>
+        <v>160953.33999999997</v>
       </c>
       <c r="T30" s="10">
         <f>-T27</f>
-        <v>173207.17999999996</v>
+        <v>169813.17000000004</v>
       </c>
       <c r="U30" s="10">
         <f>-U27</f>
-        <v>184194.94</v>
+        <v>183269.97000000003</v>
       </c>
       <c r="V30" s="10">
         <f>-V27</f>
-        <v>165698.36000000002</v>
+        <v>161614.26</v>
       </c>
       <c r="W30" s="10">
         <f>-W27</f>
-        <v>175516.76</v>
+        <v>176680.21999999997</v>
       </c>
       <c r="X30" s="10">
         <f>-X27</f>
@@ -4280,10 +4433,10 @@
     </row>
     <row r="31" spans="1:35">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C31" s="10">
         <v>4</v>
@@ -4387,7 +4540,7 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4408,187 +4561,187 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C5" s="10">
         <v>13</v>
       </c>
       <c r="D5" s="10">
-        <v>9937</v>
+        <v>10087</v>
       </c>
       <c r="E5" s="10">
         <f>D5*12</f>
-        <v>119244</v>
+        <v>121044</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C6" s="10">
         <v>14</v>
       </c>
       <c r="D6" s="10">
-        <v>10736</v>
+        <v>10535</v>
       </c>
       <c r="E6" s="10">
         <f>D6*12</f>
-        <v>128832</v>
+        <v>126420</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C7" s="10">
         <v>21</v>
       </c>
       <c r="D7" s="10">
-        <v>14079</v>
+        <v>13985</v>
       </c>
       <c r="E7" s="10">
         <f>D7*12</f>
-        <v>168948</v>
+        <v>167820</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C8" s="10">
         <v>32</v>
       </c>
       <c r="D8" s="10">
-        <v>54169</v>
+        <v>54072</v>
       </c>
       <c r="E8" s="10">
         <f>D8*12</f>
-        <v>650028</v>
+        <v>648864</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C9" s="10">
         <v>36</v>
       </c>
       <c r="D9" s="10">
-        <v>24114</v>
+        <v>24211</v>
       </c>
       <c r="E9" s="10">
         <f>D9*12</f>
-        <v>289368</v>
+        <v>290532</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C10" s="10">
         <v>40</v>
       </c>
       <c r="D10" s="10">
-        <v>27010</v>
+        <v>26755</v>
       </c>
       <c r="E10" s="10">
         <f>D10*12</f>
-        <v>324120</v>
+        <v>321060</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
         <v>133</v>
-      </c>
-      <c r="B11" t="s">
-        <v>126</v>
       </c>
       <c r="C11" s="10">
         <v>56</v>
       </c>
       <c r="D11" s="10">
-        <v>31694</v>
+        <v>32094</v>
       </c>
       <c r="E11" s="10">
         <f>D11*12</f>
-        <v>380328</v>
+        <v>385128</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(C5:C11)</f>
@@ -4605,10 +4758,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C13" s="10">
         <v>1</v>
@@ -4621,15 +4774,15 @@
         <v>180000</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C14" s="10">
         <v>19</v>
@@ -4641,12 +4794,12 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E15" s="6">
         <f>E12+E13+E14</f>
@@ -4655,327 +4808,327 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C19" s="10">
-        <v>2645</v>
+        <v>2651</v>
       </c>
       <c r="D19" s="10">
         <v>0</v>
       </c>
       <c r="E19" s="10">
         <f>(C19+D19)*12</f>
-        <v>31740</v>
+        <v>31812</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C20" s="10">
-        <v>6790</v>
+        <v>6828</v>
       </c>
       <c r="D20" s="10">
         <v>0</v>
       </c>
       <c r="E20" s="10">
         <f>(C20+D20)*12</f>
-        <v>81480</v>
+        <v>81936</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C21" s="10">
-        <v>9934</v>
+        <v>10024</v>
       </c>
       <c r="D21" s="10">
         <v>0</v>
       </c>
       <c r="E21" s="10">
         <f>(C21+D21)*12</f>
-        <v>119208</v>
+        <v>120288</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C22" s="10">
-        <v>12279</v>
+        <v>12366</v>
       </c>
       <c r="D22" s="10">
         <v>0</v>
       </c>
       <c r="E22" s="10">
         <f>(C22+D22)*12</f>
-        <v>147348</v>
+        <v>148392</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C23" s="10">
-        <v>16072</v>
+        <v>16059</v>
       </c>
       <c r="D23" s="10">
         <v>0</v>
       </c>
       <c r="E23" s="10">
         <f>(C23+D23)*12</f>
-        <v>192864</v>
+        <v>192708</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C24" s="10">
-        <v>19516</v>
+        <v>19462</v>
       </c>
       <c r="D24" s="10">
         <v>0</v>
       </c>
       <c r="E24" s="10">
         <f>(C24+D24)*12</f>
-        <v>234192</v>
+        <v>233544</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C25" s="10">
-        <v>23110</v>
+        <v>23092</v>
       </c>
       <c r="D25" s="10">
         <v>0</v>
       </c>
       <c r="E25" s="10">
         <f>(C25+D25)*12</f>
-        <v>277320</v>
+        <v>277104</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C26" s="10">
-        <v>28651</v>
+        <v>28610</v>
       </c>
       <c r="D26" s="10">
         <v>0</v>
       </c>
       <c r="E26" s="10">
         <f>(C26+D26)*12</f>
-        <v>343812</v>
+        <v>343320</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C27" s="10">
-        <v>34642</v>
+        <v>34539</v>
       </c>
       <c r="D27" s="10">
         <v>0</v>
       </c>
       <c r="E27" s="10">
         <f>(C27+D27)*12</f>
-        <v>415704</v>
+        <v>414468</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C28" s="10">
-        <v>40682</v>
+        <v>40585</v>
       </c>
       <c r="D28" s="10">
         <v>0</v>
       </c>
       <c r="E28" s="10">
         <f>(C28+D28)*12</f>
-        <v>488184</v>
+        <v>487020</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C29" s="10">
-        <v>65971</v>
+        <v>65867</v>
       </c>
       <c r="D29" s="10">
         <v>0</v>
       </c>
       <c r="E29" s="10">
         <f>(C29+D29)*12</f>
-        <v>791652</v>
+        <v>790404</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C30" s="10">
-        <v>72859</v>
+        <v>72656</v>
       </c>
       <c r="D30" s="10">
         <v>0</v>
       </c>
       <c r="E30" s="10">
         <f>(C30+D30)*12</f>
-        <v>874308</v>
+        <v>871872</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C31" s="10">
-        <v>77249</v>
+        <v>77134</v>
       </c>
       <c r="D31" s="10">
         <v>0</v>
       </c>
       <c r="E31" s="10">
         <f>(C31+D31)*12</f>
-        <v>926988</v>
+        <v>925608</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C32" s="10">
-        <v>85735</v>
+        <v>85778</v>
       </c>
       <c r="D32" s="10">
         <v>0</v>
       </c>
       <c r="E32" s="10">
         <f>(C32+D32)*12</f>
-        <v>1028820</v>
+        <v>1029336</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C33" s="10">
-        <v>95975</v>
+        <v>95824</v>
       </c>
       <c r="D33" s="10">
         <v>0</v>
       </c>
       <c r="E33" s="10">
         <f>(C33+D33)*12</f>
-        <v>1151700</v>
+        <v>1149888</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C34" s="10">
-        <v>122963</v>
+        <v>122664</v>
       </c>
       <c r="D34" s="10">
         <v>0</v>
       </c>
       <c r="E34" s="10">
         <f>(C34+D34)*12</f>
-        <v>1475556</v>
+        <v>1471968</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C35" s="10">
-        <v>133950</v>
+        <v>133652</v>
       </c>
       <c r="D35" s="10">
         <v>0</v>
       </c>
       <c r="E35" s="10">
         <f>(C35+D35)*12</f>
-        <v>1607400</v>
+        <v>1603824</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C36" s="10">
-        <v>142837</v>
+        <v>142497</v>
       </c>
       <c r="D36" s="10">
         <v>0</v>
       </c>
       <c r="E36" s="10">
         <f>(C36+D36)*12</f>
-        <v>1714044</v>
+        <v>1709964</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C37" s="10">
-        <v>150175</v>
+        <v>149831</v>
       </c>
       <c r="D37" s="10">
         <v>0</v>
       </c>
       <c r="E37" s="10">
         <f>(C37+D37)*12</f>
-        <v>1802100</v>
+        <v>1797972</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C38" s="10">
-        <v>161257</v>
+        <v>160971</v>
       </c>
       <c r="D38" s="10">
         <v>15000</v>
       </c>
       <c r="E38" s="10">
         <f>(C38+D38)*12</f>
-        <v>2115084</v>
+        <v>2111652</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C39" s="10">
         <v>171739</v>
@@ -4990,7 +5143,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5010,86 +5163,86 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B5" s="10">
         <v>4</v>
       </c>
       <c r="C5" s="10">
-        <v>2296</v>
+        <v>2302</v>
       </c>
       <c r="D5" s="10">
-        <v>1947</v>
+        <v>1953</v>
       </c>
       <c r="E5" s="12">
         <f>D5/C5</f>
-        <v>0.8479965156794426</v>
+        <v>0.8483927019982623</v>
       </c>
       <c r="F5" s="12">
         <v>1</v>
@@ -5119,34 +5272,34 @@
         <v>1</v>
       </c>
       <c r="O5" s="12">
-        <v>0.8479965156794426</v>
+        <v>0.8483927019982623</v>
       </c>
       <c r="P5" s="12">
-        <v>0.8479965156794426</v>
+        <v>0.8483927019982623</v>
       </c>
       <c r="Q5" s="12">
-        <v>0.8479965156794426</v>
+        <v>0.8483927019982623</v>
       </c>
       <c r="R5" s="12">
-        <v>0.8479965156794426</v>
+        <v>0.8483927019982623</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B6" s="10">
         <v>6</v>
       </c>
       <c r="C6" s="10">
-        <v>4494</v>
+        <v>4526</v>
       </c>
       <c r="D6" s="10">
-        <v>5244</v>
+        <v>5276</v>
       </c>
       <c r="E6" s="12">
         <f>D6/C6</f>
-        <v>1.1668891855807744</v>
+        <v>1.16570923552806</v>
       </c>
       <c r="F6" s="12">
         <v>1</v>
@@ -5167,43 +5320,43 @@
         <v>1</v>
       </c>
       <c r="L6" s="12">
-        <v>1.06675567423231</v>
+        <v>1.066283694211224</v>
       </c>
       <c r="M6" s="12">
-        <v>1.06675567423231</v>
+        <v>1.066283694211224</v>
       </c>
       <c r="N6" s="12">
-        <v>1.06675567423231</v>
+        <v>1.066283694211224</v>
       </c>
       <c r="O6" s="12">
-        <v>1.06675567423231</v>
+        <v>1.066283694211224</v>
       </c>
       <c r="P6" s="12">
-        <v>1.166889185580774</v>
+        <v>1.16570923552806</v>
       </c>
       <c r="Q6" s="12">
-        <v>1.166889185580774</v>
+        <v>1.16570923552806</v>
       </c>
       <c r="R6" s="12">
-        <v>1.166889185580774</v>
+        <v>1.16570923552806</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B7" s="10">
         <v>4</v>
       </c>
       <c r="C7" s="10">
-        <v>1396</v>
+        <v>1448</v>
       </c>
       <c r="D7" s="10">
-        <v>1996</v>
+        <v>2063</v>
       </c>
       <c r="E7" s="12">
         <f>D7/C7</f>
-        <v>1.4297994269340975</v>
+        <v>1.4247237569060773</v>
       </c>
       <c r="F7" s="12">
         <v>1</v>
@@ -5233,34 +5386,34 @@
         <v>1</v>
       </c>
       <c r="O7" s="12">
-        <v>1.214899713467049</v>
+        <v>1.207182320441989</v>
       </c>
       <c r="P7" s="12">
-        <v>1.429799426934097</v>
+        <v>1.424723756906077</v>
       </c>
       <c r="Q7" s="12">
-        <v>1.429799426934097</v>
+        <v>1.424723756906077</v>
       </c>
       <c r="R7" s="12">
-        <v>1.429799426934097</v>
+        <v>1.424723756906077</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B8" s="10">
         <v>7</v>
       </c>
       <c r="C8" s="10">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="D8" s="10">
-        <v>4344</v>
+        <v>4311</v>
       </c>
       <c r="E8" s="12">
         <f>D8/C8</f>
-        <v>1.0613242120693867</v>
+        <v>1.0540342298288508</v>
       </c>
       <c r="F8" s="12">
         <v>1</v>
@@ -5272,52 +5425,52 @@
         <v>1</v>
       </c>
       <c r="I8" s="12">
-        <v>0.8414365990715856</v>
+        <v>0.841320293398533</v>
       </c>
       <c r="J8" s="12">
-        <v>0.9147324700708527</v>
+        <v>0.9146699266503667</v>
       </c>
       <c r="K8" s="12">
-        <v>0.9147324700708527</v>
+        <v>0.9146699266503667</v>
       </c>
       <c r="L8" s="12">
-        <v>0.9147324700708527</v>
+        <v>0.9146699266503667</v>
       </c>
       <c r="M8" s="12">
-        <v>1.061324212069387</v>
+        <v>1.054034229828851</v>
       </c>
       <c r="N8" s="12">
-        <v>1.061324212069387</v>
+        <v>1.054034229828851</v>
       </c>
       <c r="O8" s="12">
-        <v>1.061324212069387</v>
+        <v>1.054034229828851</v>
       </c>
       <c r="P8" s="12">
-        <v>1.061324212069387</v>
+        <v>1.054034229828851</v>
       </c>
       <c r="Q8" s="12">
-        <v>1.061324212069387</v>
+        <v>1.054034229828851</v>
       </c>
       <c r="R8" s="12">
-        <v>1.061324212069387</v>
+        <v>1.054034229828851</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B9" s="10">
         <v>5</v>
       </c>
       <c r="C9" s="10">
-        <v>3095</v>
+        <v>2995</v>
       </c>
       <c r="D9" s="10">
-        <v>2446</v>
+        <v>2346</v>
       </c>
       <c r="E9" s="12">
         <f>D9/C9</f>
-        <v>0.7903069466882068</v>
+        <v>0.78330550918197</v>
       </c>
       <c r="F9" s="12">
         <v>1</v>
@@ -5341,40 +5494,40 @@
         <v>1</v>
       </c>
       <c r="M9" s="12">
-        <v>0.6449111470113086</v>
+        <v>0.6330550918196995</v>
       </c>
       <c r="N9" s="12">
-        <v>0.6449111470113086</v>
+        <v>0.6330550918196995</v>
       </c>
       <c r="O9" s="12">
-        <v>0.6449111470113086</v>
+        <v>0.6330550918196995</v>
       </c>
       <c r="P9" s="12">
-        <v>0.6449111470113086</v>
+        <v>0.6330550918196995</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.7903069466882068</v>
+        <v>0.78330550918197</v>
       </c>
       <c r="R9" s="12">
-        <v>0.7903069466882068</v>
+        <v>0.78330550918197</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B10" s="10">
         <v>6</v>
       </c>
       <c r="C10" s="10">
-        <v>3144</v>
+        <v>3103</v>
       </c>
       <c r="D10" s="10">
-        <v>3894</v>
+        <v>3856</v>
       </c>
       <c r="E10" s="12">
         <f>D10/C10</f>
-        <v>1.2385496183206106</v>
+        <v>1.2426683854334515</v>
       </c>
       <c r="F10" s="12">
         <v>1</v>
@@ -5413,25 +5566,25 @@
         <v>1</v>
       </c>
       <c r="R10" s="12">
-        <v>1.238549618320611</v>
+        <v>1.242668385433451</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B11" s="10">
         <v>8</v>
       </c>
       <c r="C11" s="10">
-        <v>4892</v>
+        <v>4928</v>
       </c>
       <c r="D11" s="10">
-        <v>4044</v>
+        <v>4125</v>
       </c>
       <c r="E11" s="12">
         <f>D11/C11</f>
-        <v>0.8266557645134914</v>
+        <v>0.8370535714285714</v>
       </c>
       <c r="F11" s="12">
         <v>1</v>
@@ -5440,108 +5593,108 @@
         <v>1</v>
       </c>
       <c r="H11" s="12">
-        <v>1.061324611610793</v>
+        <v>1.070008116883117</v>
       </c>
       <c r="I11" s="12">
-        <v>1.061324611610793</v>
+        <v>1.070008116883117</v>
       </c>
       <c r="J11" s="12">
-        <v>1.061324611610793</v>
+        <v>1.070008116883117</v>
       </c>
       <c r="K11" s="12">
-        <v>1.061324611610793</v>
+        <v>1.070008116883117</v>
       </c>
       <c r="L11" s="12">
-        <v>1.061324611610793</v>
+        <v>1.070008116883117</v>
       </c>
       <c r="M11" s="12">
-        <v>1.061324611610793</v>
+        <v>1.070008116883117</v>
       </c>
       <c r="N11" s="12">
-        <v>1.05130825838103</v>
+        <v>1.060064935064935</v>
       </c>
       <c r="O11" s="12">
-        <v>1.05130825838103</v>
+        <v>1.060064935064935</v>
       </c>
       <c r="P11" s="12">
-        <v>1.05130825838103</v>
+        <v>1.060064935064935</v>
       </c>
       <c r="Q11" s="12">
-        <v>1.05130825838103</v>
+        <v>1.060064935064935</v>
       </c>
       <c r="R11" s="12">
-        <v>0.8266557645134914</v>
+        <v>0.8370535714285714</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B12" s="10">
         <v>8</v>
       </c>
       <c r="C12" s="10">
-        <v>4292</v>
+        <v>4301</v>
       </c>
       <c r="D12" s="10">
-        <v>4644</v>
+        <v>4608</v>
       </c>
       <c r="E12" s="12">
         <f>D12/C12</f>
-        <v>1.082013047530289</v>
+        <v>1.0713787491281097</v>
       </c>
       <c r="F12" s="12">
         <v>1</v>
       </c>
       <c r="G12" s="12">
-        <v>1.069897483690587</v>
+        <v>1.069751220646361</v>
       </c>
       <c r="H12" s="12">
-        <v>1.174743709226468</v>
+        <v>1.174378051615903</v>
       </c>
       <c r="I12" s="12">
-        <v>1.023532152842498</v>
+        <v>1.023482910950942</v>
       </c>
       <c r="J12" s="12">
-        <v>1.023532152842498</v>
+        <v>1.023482910950942</v>
       </c>
       <c r="K12" s="12">
-        <v>1.023532152842498</v>
+        <v>1.023482910950942</v>
       </c>
       <c r="L12" s="12">
-        <v>1.023532152842498</v>
+        <v>1.023482910950942</v>
       </c>
       <c r="M12" s="12">
-        <v>0.8723205964585274</v>
+        <v>0.87258777028598</v>
       </c>
       <c r="N12" s="12">
-        <v>0.9771668219944082</v>
+        <v>0.9667519181585678</v>
       </c>
       <c r="O12" s="12">
-        <v>1.082013047530289</v>
+        <v>1.07137874912811</v>
       </c>
       <c r="P12" s="12">
-        <v>1.082013047530289</v>
+        <v>1.07137874912811</v>
       </c>
       <c r="Q12" s="12">
-        <v>1.082013047530289</v>
+        <v>1.07137874912811</v>
       </c>
       <c r="R12" s="12">
-        <v>1.082013047530289</v>
+        <v>1.07137874912811</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B13" s="10">
         <v>9</v>
       </c>
       <c r="C13" s="10">
-        <v>5391</v>
+        <v>5252</v>
       </c>
       <c r="D13" s="10">
-        <v>5391</v>
+        <v>5252</v>
       </c>
       <c r="E13" s="12">
         <f>D13/C13</f>
@@ -5589,7 +5742,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B14" s="11">
         <f>SUM(B5:B13)</f>
@@ -5597,20 +5750,20 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C5:C13)</f>
-        <v>33093</v>
+        <v>32945</v>
       </c>
       <c r="D14" s="11">
         <f>SUM(D5:D13)</f>
-        <v>33950</v>
+        <v>33790</v>
       </c>
       <c r="E14" s="7">
         <f>D14/C14</f>
-        <v>1.0258967153174388</v>
+        <v>1.025648808620428</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5630,178 +5783,178 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D5" s="10">
-        <v>190000</v>
+        <v>191000</v>
       </c>
       <c r="E5" s="10">
         <f>D5*LOAD_FACTOR/12</f>
-        <v>20266.666666666668</v>
+        <v>20373.333333333332</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D6" s="10">
-        <v>140000</v>
+        <v>139000</v>
       </c>
       <c r="E6" s="10">
         <f>D6*LOAD_FACTOR/12</f>
-        <v>14933.333333333334</v>
+        <v>14826.666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D7" s="10">
-        <v>185000</v>
+        <v>189000</v>
       </c>
       <c r="E7" s="10">
         <f>D7*LOAD_FACTOR/12</f>
-        <v>19733.333333333332</v>
+        <v>20160.0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D8" s="10">
-        <v>145000</v>
+        <v>141000</v>
       </c>
       <c r="E8" s="10">
         <f>D8*LOAD_FACTOR/12</f>
-        <v>15466.666666666666</v>
+        <v>15040.0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D9" s="10">
-        <v>175000</v>
+        <v>173500</v>
       </c>
       <c r="E9" s="10">
         <f>D9*LOAD_FACTOR/12</f>
-        <v>18666.666666666668</v>
+        <v>18506.666666666668</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D10" s="10">
-        <v>155000</v>
+        <v>156500</v>
       </c>
       <c r="E10" s="10">
         <f>D10*LOAD_FACTOR/12</f>
-        <v>16533.333333333332</v>
+        <v>16693.333333333332</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D11" s="10">
-        <v>215000</v>
+        <v>211000</v>
       </c>
       <c r="E11" s="10">
         <f>D11*LOAD_FACTOR/12</f>
-        <v>22933.333333333332</v>
+        <v>22506.666666666668</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D12" s="10">
-        <v>115000</v>
+        <v>119000</v>
       </c>
       <c r="E12" s="10">
         <f>D12*LOAD_FACTOR/12</f>
-        <v>12266.666666666666</v>
+        <v>12693.333333333334</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B13" s="6">
         <f>COUNTA(A5:A12)</f>
@@ -5810,7 +5963,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B14" s="10">
         <f>STAFF_NOW+B13</f>
@@ -5819,7 +5972,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5829,7 +5982,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.7109375" customWidth="1"/>
@@ -5838,30 +5991,30 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B3" s="6">
-        <f>COUNTIF(J9:J56,"&gt;0")</f>
+        <f>COUNTIF(J9:J68,"&gt;0")</f>
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B4" s="6">
         <f>AVERAGE(H9:H20)</f>
-        <v>374461.8123726681</v>
+        <v>374461.81237266795</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="6">
         <f>CASH_START</f>
@@ -5870,39 +6023,39 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B8" s="10">
         <v>0</v>
@@ -5914,7 +6067,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B9" s="10">
         <v>1</v>
@@ -5948,7 +6101,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B10" s="10">
         <v>2</v>
@@ -5982,7 +6135,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B11" s="10">
         <v>3</v>
@@ -5994,7 +6147,7 @@
         <v>41408.17345192499</v>
       </c>
       <c r="E11" s="10">
-        <v>359466.6666666667</v>
+        <v>359466.6666666666</v>
       </c>
       <c r="F11" s="10">
         <v>80541.29000000001</v>
@@ -6004,19 +6157,19 @@
       </c>
       <c r="H11" s="10">
         <f>D11+E11+F11+G11-C11</f>
-        <v>274375.2628589667</v>
+        <v>274375.2628589666</v>
       </c>
       <c r="I11" s="10">
         <v>0</v>
       </c>
       <c r="J11" s="10">
         <f>J10+I11-H11</f>
-        <v>1065860.3040276999</v>
+        <v>1065860.3040277</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B12" s="10">
         <v>4</v>
@@ -6028,7 +6181,7 @@
         <v>42857.45952274236</v>
       </c>
       <c r="E12" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F12" s="10">
         <v>80541.29000000001</v>
@@ -6038,19 +6191,19 @@
       </c>
       <c r="H12" s="10">
         <f>D12+E12+F12+G12-C12</f>
-        <v>443778.1185756972</v>
+        <v>443778.11857569707</v>
       </c>
       <c r="I12" s="10">
         <v>9000000</v>
       </c>
       <c r="J12" s="10">
         <f>J11+I12-H12</f>
-        <v>9622082.185452001</v>
+        <v>9622082.185452003</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B13" s="10">
         <v>5</v>
@@ -6062,7 +6215,7 @@
         <v>44357.47060603835</v>
       </c>
       <c r="E13" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F13" s="10">
         <v>80541.29000000001</v>
@@ -6072,19 +6225,19 @@
       </c>
       <c r="H13" s="10">
         <f>D13+E13+F13+G13-C13</f>
-        <v>437778.0742425133</v>
+        <v>437778.07424251316</v>
       </c>
       <c r="I13" s="10">
         <v>0</v>
       </c>
       <c r="J13" s="10">
         <f>J12+I13-H13</f>
-        <v>9184304.111209488</v>
+        <v>9184304.11120949</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B14" s="10">
         <v>6</v>
@@ -6096,7 +6249,7 @@
         <v>45909.98207724969</v>
       </c>
       <c r="E14" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F14" s="10">
         <v>80541.29000000001</v>
@@ -6106,19 +6259,19 @@
       </c>
       <c r="H14" s="10">
         <f>D14+E14+F14+G14-C14</f>
-        <v>431568.0283576679</v>
+        <v>431568.0283576678</v>
       </c>
       <c r="I14" s="10">
         <v>0</v>
       </c>
       <c r="J14" s="10">
         <f>J13+I14-H14</f>
-        <v>8752736.08285182</v>
+        <v>8752736.082851822</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B15" s="10">
         <v>7</v>
@@ -6130,7 +6283,7 @@
         <v>47516.83144995342</v>
       </c>
       <c r="E15" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F15" s="10">
         <v>80541.29000000001</v>
@@ -6140,19 +6293,19 @@
       </c>
       <c r="H15" s="10">
         <f>D15+E15+F15+G15-C15</f>
-        <v>425140.63086685294</v>
+        <v>425140.6308668528</v>
       </c>
       <c r="I15" s="10">
         <v>0</v>
       </c>
       <c r="J15" s="10">
         <f>J14+I15-H15</f>
-        <v>8327595.451984967</v>
+        <v>8327595.451984969</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B16" s="10">
         <v>8</v>
@@ -6164,7 +6317,7 @@
         <v>49179.92055070178</v>
       </c>
       <c r="E16" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F16" s="10">
         <v>80541.29000000001</v>
@@ -6174,19 +6327,19 @@
       </c>
       <c r="H16" s="10">
         <f>D16+E16+F16+G16-C16</f>
-        <v>418488.2744638595</v>
+        <v>418488.2744638594</v>
       </c>
       <c r="I16" s="10">
         <v>0</v>
       </c>
       <c r="J16" s="10">
         <f>J15+I16-H16</f>
-        <v>7909107.177521108</v>
+        <v>7909107.17752111</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B17" s="10">
         <v>9</v>
@@ -6198,7 +6351,7 @@
         <v>50901.21776997635</v>
       </c>
       <c r="E17" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F17" s="10">
         <v>80541.29000000001</v>
@@ -6208,19 +6361,19 @@
       </c>
       <c r="H17" s="10">
         <f>D17+E17+F17+G17-C17</f>
-        <v>411603.0855867613</v>
+        <v>411603.0855867612</v>
       </c>
       <c r="I17" s="10">
         <v>0</v>
       </c>
       <c r="J17" s="10">
         <f>J16+I17-H17</f>
-        <v>7497504.091934347</v>
+        <v>7497504.091934348</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B18" s="10">
         <v>10</v>
@@ -6232,7 +6385,7 @@
         <v>52682.76039192551</v>
       </c>
       <c r="E18" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F18" s="10">
         <v>80541.29000000001</v>
@@ -6242,19 +6395,19 @@
       </c>
       <c r="H18" s="10">
         <f>D18+E18+F18+G18-C18</f>
-        <v>404476.9150989646</v>
+        <v>404476.91509896447</v>
       </c>
       <c r="I18" s="10">
         <v>0</v>
       </c>
       <c r="J18" s="10">
         <f>J17+I18-H18</f>
-        <v>7093027.176835382</v>
+        <v>7093027.176835384</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B19" s="10">
         <v>11</v>
@@ -6266,7 +6419,7 @@
         <v>54526.6570056429</v>
       </c>
       <c r="E19" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F19" s="10">
         <v>80541.29000000001</v>
@@ -6276,19 +6429,19 @@
       </c>
       <c r="H19" s="10">
         <f>D19+E19+F19+G19-C19</f>
-        <v>397101.32864409505</v>
+        <v>397101.32864409493</v>
       </c>
       <c r="I19" s="10">
         <v>0</v>
       </c>
       <c r="J19" s="10">
         <f>J18+I19-H19</f>
-        <v>6695925.848191287</v>
+        <v>6695925.848191289</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B20" s="10">
         <v>12</v>
@@ -6300,7 +6453,7 @@
         <v>56435.0900008404</v>
       </c>
       <c r="E20" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F20" s="10">
         <v>80541.29000000001</v>
@@ -6310,19 +6463,19 @@
       </c>
       <c r="H20" s="10">
         <f>D20+E20+F20+G20-C20</f>
-        <v>389467.596663305</v>
+        <v>389467.5966633049</v>
       </c>
       <c r="I20" s="10">
         <v>0</v>
       </c>
       <c r="J20" s="10">
         <f>J19+I20-H20</f>
-        <v>6306458.251527983</v>
+        <v>6306458.251527985</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B21" s="10">
         <v>13</v>
@@ -6334,7 +6487,7 @@
         <v>58410.31815086982</v>
       </c>
       <c r="E21" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F21" s="10">
         <v>80541.29000000001</v>
@@ -6344,19 +6497,19 @@
       </c>
       <c r="H21" s="10">
         <f>D21+E21+F21+G21-C21</f>
-        <v>381566.6840631874</v>
+        <v>381566.6840631873</v>
       </c>
       <c r="I21" s="10">
         <v>0</v>
       </c>
       <c r="J21" s="10">
         <f>J20+I21-H21</f>
-        <v>5924891.567464795</v>
+        <v>5924891.567464798</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B22" s="10">
         <v>14</v>
@@ -6368,7 +6521,7 @@
         <v>60454.67928615025</v>
       </c>
       <c r="E22" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F22" s="10">
         <v>80541.29000000001</v>
@@ -6378,19 +6531,19 @@
       </c>
       <c r="H22" s="10">
         <f>D22+E22+F22+G22-C22</f>
-        <v>373389.2395220657</v>
+        <v>373389.23952206556</v>
       </c>
       <c r="I22" s="10">
         <v>0</v>
       </c>
       <c r="J22" s="10">
         <f>J21+I22-H22</f>
-        <v>5551502.327942729</v>
+        <v>5551502.327942732</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B23" s="10">
         <v>15</v>
@@ -6402,7 +6555,7 @@
         <v>62570.5930611655</v>
       </c>
       <c r="E23" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F23" s="10">
         <v>80541.29000000001</v>
@@ -6412,19 +6565,19 @@
       </c>
       <c r="H23" s="10">
         <f>D23+E23+F23+G23-C23</f>
-        <v>364925.5844220047</v>
+        <v>364925.5844220046</v>
       </c>
       <c r="I23" s="10">
         <v>0</v>
       </c>
       <c r="J23" s="10">
         <f>J22+I23-H23</f>
-        <v>5186576.743520725</v>
+        <v>5186576.743520727</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B24" s="10">
         <v>16</v>
@@ -6436,7 +6589,7 @@
         <v>64760.56381830628</v>
       </c>
       <c r="E24" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F24" s="10">
         <v>80541.29000000001</v>
@@ -6446,19 +6599,19 @@
       </c>
       <c r="H24" s="10">
         <f>D24+E24+F24+G24-C24</f>
-        <v>356165.70139344153</v>
+        <v>356165.7013934414</v>
       </c>
       <c r="I24" s="10">
         <v>0</v>
       </c>
       <c r="J24" s="10">
         <f>J23+I24-H24</f>
-        <v>4830411.042127283</v>
+        <v>4830411.042127286</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B25" s="10">
         <v>17</v>
@@ -6470,7 +6623,7 @@
         <v>67027.183551947</v>
       </c>
       <c r="E25" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F25" s="10">
         <v>80541.29000000001</v>
@@ -6480,19 +6633,19 @@
       </c>
       <c r="H25" s="10">
         <f>D25+E25+F25+G25-C25</f>
-        <v>347099.22245887865</v>
+        <v>347099.22245887853</v>
       </c>
       <c r="I25" s="10">
         <v>0</v>
       </c>
       <c r="J25" s="10">
         <f>J24+I25-H25</f>
-        <v>4483311.819668405</v>
+        <v>4483311.819668408</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B26" s="10">
         <v>18</v>
@@ -6504,7 +6657,7 @@
         <v>69373.13497626515</v>
       </c>
       <c r="E26" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F26" s="10">
         <v>80541.29000000001</v>
@@ -6514,19 +6667,19 @@
       </c>
       <c r="H26" s="10">
         <f>D26+E26+F26+G26-C26</f>
-        <v>337715.41676160606</v>
+        <v>337715.41676160594</v>
       </c>
       <c r="I26" s="10">
         <v>0</v>
       </c>
       <c r="J26" s="10">
         <f>J25+I26-H26</f>
-        <v>4145596.4029067988</v>
+        <v>4145596.4029068016</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B27" s="10">
         <v>19</v>
@@ -6538,7 +6691,7 @@
         <v>71801.19470043443</v>
       </c>
       <c r="E27" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F27" s="10">
         <v>80541.29000000001</v>
@@ -6548,19 +6701,19 @@
       </c>
       <c r="H27" s="10">
         <f>D27+E27+F27+G27-C27</f>
-        <v>328003.177864929</v>
+        <v>328003.1778649289</v>
       </c>
       <c r="I27" s="10">
         <v>0</v>
       </c>
       <c r="J27" s="10">
         <f>J26+I27-H27</f>
-        <v>3817593.2250418696</v>
+        <v>3817593.225041873</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B28" s="10">
         <v>20</v>
@@ -6572,7 +6725,7 @@
         <v>74314.23651494962</v>
       </c>
       <c r="E28" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F28" s="10">
         <v>80541.29000000001</v>
@@ -6582,19 +6735,19 @@
       </c>
       <c r="H28" s="10">
         <f>D28+E28+F28+G28-C28</f>
-        <v>317951.01060686813</v>
+        <v>317951.010606868</v>
       </c>
       <c r="I28" s="10">
         <v>0</v>
       </c>
       <c r="J28" s="10">
         <f>J27+I28-H28</f>
-        <v>3499642.2144350014</v>
+        <v>3499642.2144350046</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B29" s="10">
         <v>21</v>
@@ -6606,7 +6759,7 @@
         <v>76915.23479297286</v>
       </c>
       <c r="E29" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F29" s="10">
         <v>80541.29000000001</v>
@@ -6623,12 +6776,12 @@
       </c>
       <c r="J29" s="10">
         <f>J28+I29-H29</f>
-        <v>3192095.196940226</v>
+        <v>3192095.1969402293</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B30" s="10">
         <v>22</v>
@@ -6640,7 +6793,7 @@
         <v>79607.2680107269</v>
       </c>
       <c r="E30" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F30" s="10">
         <v>80541.29000000001</v>
@@ -6650,19 +6803,19 @@
       </c>
       <c r="H30" s="10">
         <f>D30+E30+F30+G30-C30</f>
-        <v>296778.8846237591</v>
+        <v>296778.88462375896</v>
       </c>
       <c r="I30" s="10">
         <v>0</v>
       </c>
       <c r="J30" s="10">
         <f>J29+I30-H30</f>
-        <v>2895316.312316467</v>
+        <v>2895316.3123164703</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B31" s="10">
         <v>23</v>
@@ -6674,7 +6827,7 @@
         <v>82393.52239110233</v>
       </c>
       <c r="E31" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F31" s="10">
         <v>80541.29000000001</v>
@@ -6684,19 +6837,19 @@
       </c>
       <c r="H31" s="10">
         <f>D31+E31+F31+G31-C31</f>
-        <v>285633.8671022574</v>
+        <v>285633.86710225715</v>
       </c>
       <c r="I31" s="10">
         <v>0</v>
       </c>
       <c r="J31" s="10">
         <f>J30+I31-H31</f>
-        <v>2609682.4452142096</v>
+        <v>2609682.4452142133</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B32" s="10">
         <v>24</v>
@@ -6708,7 +6861,7 @@
         <v>85277.2956747909</v>
       </c>
       <c r="E32" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F32" s="10">
         <v>80541.29000000001</v>
@@ -6718,19 +6871,19 @@
       </c>
       <c r="H32" s="10">
         <f>D32+E32+F32+G32-C32</f>
-        <v>274098.773967503</v>
+        <v>274098.7739675029</v>
       </c>
       <c r="I32" s="10">
         <v>0</v>
       </c>
       <c r="J32" s="10">
         <f>J31+I32-H32</f>
-        <v>2335583.6712467065</v>
+        <v>2335583.6712467102</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B33" s="10">
         <v>25</v>
@@ -6742,7 +6895,7 @@
         <v>88262.00102340859</v>
       </c>
       <c r="E33" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F33" s="10">
         <v>80541.29000000001</v>
@@ -6752,19 +6905,19 @@
       </c>
       <c r="H33" s="10">
         <f>D33+E33+F33+G33-C33</f>
-        <v>262159.95257303235</v>
+        <v>262159.95257303223</v>
       </c>
       <c r="I33" s="10">
         <v>0</v>
       </c>
       <c r="J33" s="10">
         <f>J32+I33-H33</f>
-        <v>2073423.7186736742</v>
+        <v>2073423.718673678</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B34" s="10">
         <v>26</v>
@@ -6776,7 +6929,7 @@
         <v>91351.17105922788</v>
       </c>
       <c r="E34" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F34" s="10">
         <v>80541.29000000001</v>
@@ -6786,19 +6939,19 @@
       </c>
       <c r="H34" s="10">
         <f>D34+E34+F34+G34-C34</f>
-        <v>249803.2724297552</v>
+        <v>249803.27242975507</v>
       </c>
       <c r="I34" s="10">
         <v>0</v>
       </c>
       <c r="J34" s="10">
         <f>J33+I34-H34</f>
-        <v>1823620.446243919</v>
+        <v>1823620.4462439232</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B35" s="10">
         <v>27</v>
@@ -6810,7 +6963,7 @@
         <v>94548.46204630085</v>
       </c>
       <c r="E35" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F35" s="10">
         <v>80541.29000000001</v>
@@ -6820,19 +6973,19 @@
       </c>
       <c r="H35" s="10">
         <f>D35+E35+F35+G35-C35</f>
-        <v>237014.10848146334</v>
+        <v>237014.10848146322</v>
       </c>
       <c r="I35" s="10">
         <v>0</v>
       </c>
       <c r="J35" s="10">
         <f>J34+I35-H35</f>
-        <v>1586606.3377624557</v>
+        <v>1586606.3377624599</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B36" s="10">
         <v>28</v>
@@ -6844,7 +6997,7 @@
         <v>97857.65821792137</v>
       </c>
       <c r="E36" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F36" s="10">
         <v>80541.29000000001</v>
@@ -6854,19 +7007,19 @@
       </c>
       <c r="H36" s="10">
         <f>D36+E36+F36+G36-C36</f>
-        <v>223777.32379498123</v>
+        <v>223777.32379498112</v>
       </c>
       <c r="I36" s="10">
         <v>0</v>
       </c>
       <c r="J36" s="10">
         <f>J35+I36-H36</f>
-        <v>1362829.0139674745</v>
+        <v>1362829.0139674786</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B37" s="10">
         <v>29</v>
@@ -6878,7 +7031,7 @@
         <v>101282.6762555486</v>
       </c>
       <c r="E37" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F37" s="10">
         <v>80541.29000000001</v>
@@ -6888,19 +7041,19 @@
       </c>
       <c r="H37" s="10">
         <f>D37+E37+F37+G37-C37</f>
-        <v>210077.25164447224</v>
+        <v>210077.25164447213</v>
       </c>
       <c r="I37" s="10">
         <v>0</v>
       </c>
       <c r="J37" s="10">
         <f>J36+I37-H37</f>
-        <v>1152751.7623230023</v>
+        <v>1152751.7623230065</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B38" s="10">
         <v>30</v>
@@ -6912,7 +7065,7 @@
         <v>104827.5699244928</v>
       </c>
       <c r="E38" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F38" s="10">
         <v>80541.29000000001</v>
@@ -6929,12 +7082,12 @@
       </c>
       <c r="J38" s="10">
         <f>J37+I38-H38</f>
-        <v>956854.085354307</v>
+        <v>956854.0853543112</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B39" s="10">
         <v>31</v>
@@ -6946,7 +7099,7 @@
         <v>108496.53487185</v>
       </c>
       <c r="E39" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F39" s="10">
         <v>80541.29000000001</v>
@@ -6956,19 +7109,19 @@
       </c>
       <c r="H39" s="10">
         <f>D39+E39+F39+G39-C39</f>
-        <v>181221.81717926648</v>
+        <v>181221.81717926636</v>
       </c>
       <c r="I39" s="10">
         <v>0</v>
       </c>
       <c r="J39" s="10">
         <f>J38+I39-H39</f>
-        <v>775632.2681750405</v>
+        <v>775632.2681750448</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B40" s="10">
         <v>32</v>
@@ -6980,7 +7133,7 @@
         <v>112293.9135923648</v>
       </c>
       <c r="E40" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F40" s="10">
         <v>80541.29000000001</v>
@@ -6990,19 +7143,19 @@
       </c>
       <c r="H40" s="10">
         <f>D40+E40+F40+G40-C40</f>
-        <v>166032.30229720753</v>
+        <v>166032.3022972074</v>
       </c>
       <c r="I40" s="10">
         <v>0</v>
       </c>
       <c r="J40" s="10">
         <f>J39+I40-H40</f>
-        <v>609599.965877833</v>
+        <v>609599.9658778374</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B41" s="10">
         <v>33</v>
@@ -7014,7 +7167,7 @@
         <v>116224.2005680975</v>
       </c>
       <c r="E41" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F41" s="10">
         <v>80541.29000000001</v>
@@ -7024,19 +7177,19 @@
       </c>
       <c r="H41" s="10">
         <f>D41+E41+F41+G41-C41</f>
-        <v>150311.15439427656</v>
+        <v>150311.15439427644</v>
       </c>
       <c r="I41" s="10">
         <v>0</v>
       </c>
       <c r="J41" s="10">
         <f>J40+I41-H41</f>
-        <v>459288.8114835564</v>
+        <v>459288.81148356094</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B42" s="10">
         <v>34</v>
@@ -7048,7 +7201,7 @@
         <v>120292.0475879809</v>
       </c>
       <c r="E42" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F42" s="10">
         <v>80541.29000000001</v>
@@ -7065,12 +7218,12 @@
       </c>
       <c r="J42" s="10">
         <f>J41+I42-H42</f>
-        <v>325249.04516881355</v>
+        <v>325249.0451688181</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B43" s="10">
         <v>35</v>
@@ -7082,7 +7235,7 @@
         <v>124502.2692535603</v>
       </c>
       <c r="E43" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F43" s="10">
         <v>80541.29000000001</v>
@@ -7092,19 +7245,19 @@
       </c>
       <c r="H43" s="10">
         <f>D43+E43+F43+G43-C43</f>
-        <v>117198.87965242565</v>
+        <v>117198.87965242553</v>
       </c>
       <c r="I43" s="10">
         <v>0</v>
       </c>
       <c r="J43" s="10">
         <f>J42+I43-H43</f>
-        <v>208050.1655163879</v>
+        <v>208050.16551639256</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B44" s="10">
         <v>36</v>
@@ -7116,7 +7269,7 @@
         <v>128859.8486774348</v>
       </c>
       <c r="E44" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F44" s="10">
         <v>80541.29000000001</v>
@@ -7126,19 +7279,19 @@
       </c>
       <c r="H44" s="10">
         <f>D44+E44+F44+G44-C44</f>
-        <v>99768.5619569273</v>
+        <v>99768.56195692718</v>
       </c>
       <c r="I44" s="10">
         <v>0</v>
       </c>
       <c r="J44" s="10">
         <f>J43+I44-H44</f>
-        <v>108281.60355946061</v>
+        <v>108281.60355946538</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B45" s="10">
         <v>37</v>
@@ -7150,7 +7303,7 @@
         <v>133369.9433811451</v>
       </c>
       <c r="E45" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F45" s="10">
         <v>80541.29000000001</v>
@@ -7167,12 +7320,12 @@
       </c>
       <c r="J45" s="10">
         <f>J44+I45-H45</f>
-        <v>26553.420417374233</v>
+        <v>26553.420417379006</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B46" s="10">
         <v>38</v>
@@ -7184,7 +7337,7 @@
         <v>138037.8913994851</v>
       </c>
       <c r="E46" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F46" s="10">
         <v>80541.29000000001</v>
@@ -7194,19 +7347,19 @@
       </c>
       <c r="H46" s="10">
         <f>D46+E46+F46+G46-C46</f>
-        <v>63056.391068726196</v>
+        <v>63056.39106872596</v>
       </c>
       <c r="I46" s="10">
         <v>0</v>
       </c>
       <c r="J46" s="10">
         <f>J45+I46-H46</f>
-        <v>-36502.97065135196</v>
+        <v>-36502.97065134696</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B47" s="10">
         <v>39</v>
@@ -7218,7 +7371,7 @@
         <v>142869.2175984671</v>
       </c>
       <c r="E47" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F47" s="10">
         <v>80541.29000000001</v>
@@ -7235,12 +7388,12 @@
       </c>
       <c r="J47" s="10">
         <f>J46+I47-H47</f>
-        <v>-80234.05692415021</v>
+        <v>-80234.0569241452</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B48" s="10">
         <v>40</v>
@@ -7252,7 +7405,7 @@
         <v>147869.6402144134</v>
       </c>
       <c r="E48" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F48" s="10">
         <v>80541.29000000001</v>
@@ -7262,19 +7415,19 @@
       </c>
       <c r="H48" s="10">
         <f>D48+E48+F48+G48-C48</f>
-        <v>23729.39580901293</v>
+        <v>23729.395809012814</v>
       </c>
       <c r="I48" s="10">
         <v>0</v>
       </c>
       <c r="J48" s="10">
         <f>J47+I48-H48</f>
-        <v>-103963.45273316314</v>
+        <v>-103963.45273315802</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B49" s="10">
         <v>41</v>
@@ -7286,7 +7439,7 @@
         <v>153045.0776219179</v>
       </c>
       <c r="E49" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F49" s="10">
         <v>80541.29000000001</v>
@@ -7303,12 +7456,12 @@
       </c>
       <c r="J49" s="10">
         <f>J48+I49-H49</f>
-        <v>-106991.09891215817</v>
+        <v>-106991.09891215304</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B50" s="10">
         <v>42</v>
@@ -7320,7 +7473,7 @@
         <v>158401.655338685</v>
       </c>
       <c r="E50" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F50" s="10">
         <v>80541.29000000001</v>
@@ -7330,19 +7483,19 @@
       </c>
       <c r="H50" s="10">
         <f>D50+E50+F50+G50-C50</f>
-        <v>-18398.66468807333</v>
+        <v>-18398.664688073448</v>
       </c>
       <c r="I50" s="10">
         <v>0</v>
       </c>
       <c r="J50" s="10">
         <f>J49+I50-H50</f>
-        <v>-88592.43422408483</v>
+        <v>-88592.4342240796</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B51" s="10">
         <v>43</v>
@@ -7354,7 +7507,7 @@
         <v>163945.713275539</v>
       </c>
       <c r="E51" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F51" s="10">
         <v>80541.29000000001</v>
@@ -7364,19 +7517,19 @@
       </c>
       <c r="H51" s="10">
         <f>D51+E51+F51+G51-C51</f>
-        <v>-40574.89643548918</v>
+        <v>-40574.896435489296</v>
       </c>
       <c r="I51" s="10">
         <v>0</v>
       </c>
       <c r="J51" s="10">
         <f>J50+I51-H51</f>
-        <v>-48017.537788595655</v>
+        <v>-48017.5377885903</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B52" s="10">
         <v>44</v>
@@ -7388,7 +7541,7 @@
         <v>169683.8132401828</v>
       </c>
       <c r="E52" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F52" s="10">
         <v>80541.29000000001</v>
@@ -7398,19 +7551,19 @@
       </c>
       <c r="H52" s="10">
         <f>D52+E52+F52+G52-C52</f>
-        <v>-63527.29629406461</v>
+        <v>-63527.29629406473</v>
       </c>
       <c r="I52" s="10">
         <v>0</v>
       </c>
       <c r="J52" s="10">
         <f>J51+I52-H52</f>
-        <v>15509.758505468955</v>
+        <v>15509.758505474427</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B53" s="10">
         <v>45</v>
@@ -7422,7 +7575,7 @@
         <v>175622.7467035892</v>
       </c>
       <c r="E53" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F53" s="10">
         <v>80541.29000000001</v>
@@ -7432,19 +7585,19 @@
       </c>
       <c r="H53" s="10">
         <f>D53+E53+F53+G53-C53</f>
-        <v>-87283.0301476901</v>
+        <v>-87283.03014769021</v>
       </c>
       <c r="I53" s="10">
         <v>0</v>
       </c>
       <c r="J53" s="10">
         <f>J52+I53-H53</f>
-        <v>102792.78865315905</v>
+        <v>102792.78865316464</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B54" s="10">
         <v>46</v>
@@ -7456,7 +7609,7 @@
         <v>181769.5428382148</v>
       </c>
       <c r="E54" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F54" s="10">
         <v>80541.29000000001</v>
@@ -7466,19 +7619,19 @@
       </c>
       <c r="H54" s="10">
         <f>D54+E54+F54+G54-C54</f>
-        <v>-111870.21468619257</v>
+        <v>-111870.21468619269</v>
       </c>
       <c r="I54" s="10">
         <v>0</v>
       </c>
       <c r="J54" s="10">
         <f>J53+I54-H54</f>
-        <v>214663.00333935162</v>
+        <v>214663.00333935732</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B55" s="10">
         <v>47</v>
@@ -7490,7 +7643,7 @@
         <v>188131.4768375523</v>
       </c>
       <c r="E55" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F55" s="10">
         <v>80541.29000000001</v>
@@ -7507,12 +7660,12 @@
       </c>
       <c r="J55" s="10">
         <f>J54+I55-H55</f>
-        <v>351980.95402289426</v>
+        <v>351980.95402289997</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B56" s="10">
         <v>48</v>
@@ -7524,7 +7677,7 @@
         <v>194716.0785268666</v>
       </c>
       <c r="E56" s="10">
-        <v>394666.6666666667</v>
+        <v>394666.6666666666</v>
       </c>
       <c r="F56" s="10">
         <v>80541.29000000001</v>
@@ -7534,19 +7687,558 @@
       </c>
       <c r="H56" s="10">
         <f>D56+E56+F56+G56-C56</f>
-        <v>-163656.35744079982</v>
+        <v>-163656.35744079994</v>
       </c>
       <c r="I56" s="10">
         <v>0</v>
       </c>
       <c r="J56" s="10">
         <f>J55+I56-H56</f>
-        <v>515637.3114636941</v>
+        <v>515637.3114636999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" s="10">
+        <v>49</v>
+      </c>
+      <c r="C57" s="10">
+        <v>1007655.706376535</v>
+      </c>
+      <c r="D57" s="10">
+        <v>201531.1412753069</v>
+      </c>
+      <c r="E57" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F57" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G57" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H57" s="10">
+        <f>D57+E57+F57+G57-C57</f>
+        <v>-190916.60843456117</v>
+      </c>
+      <c r="I57" s="10">
+        <v>0</v>
+      </c>
+      <c r="J57" s="10">
+        <f>J56+I57-H57</f>
+        <v>706553.9198982611</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="3" t="s">
-        <v>14</v>
+      <c r="A58" t="s">
+        <v>241</v>
+      </c>
+      <c r="B58" s="10">
+        <v>50</v>
+      </c>
+      <c r="C58" s="10">
+        <v>1042923.656099713</v>
+      </c>
+      <c r="D58" s="10">
+        <v>208584.7312199427</v>
+      </c>
+      <c r="E58" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F58" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G58" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H58" s="10">
+        <f>D58+E58+F58+G58-C58</f>
+        <v>-219130.96821310406</v>
+      </c>
+      <c r="I58" s="10">
+        <v>0</v>
+      </c>
+      <c r="J58" s="10">
+        <f>J57+I58-H58</f>
+        <v>925684.8881113651</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>242</v>
+      </c>
+      <c r="B59" s="10">
+        <v>51</v>
+      </c>
+      <c r="C59" s="10">
+        <v>1079425.984063203</v>
+      </c>
+      <c r="D59" s="10">
+        <v>215885.1968126406</v>
+      </c>
+      <c r="E59" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F59" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G59" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H59" s="10">
+        <f>D59+E59+F59+G59-C59</f>
+        <v>-248332.83058389602</v>
+      </c>
+      <c r="I59" s="10">
+        <v>0</v>
+      </c>
+      <c r="J59" s="10">
+        <f>J58+I59-H59</f>
+        <v>1174017.718695261</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>243</v>
+      </c>
+      <c r="B60" s="10">
+        <v>52</v>
+      </c>
+      <c r="C60" s="10">
+        <v>1117205.893505415</v>
+      </c>
+      <c r="D60" s="10">
+        <v>223441.178701083</v>
+      </c>
+      <c r="E60" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F60" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G60" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H60" s="10">
+        <f>D60+E60+F60+G60-C60</f>
+        <v>-278556.7581376656</v>
+      </c>
+      <c r="I60" s="10">
+        <v>0</v>
+      </c>
+      <c r="J60" s="10">
+        <f>J59+I60-H60</f>
+        <v>1452574.4768329267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>244</v>
+      </c>
+      <c r="B61" s="10">
+        <v>53</v>
+      </c>
+      <c r="C61" s="10">
+        <v>1156308.099778105</v>
+      </c>
+      <c r="D61" s="10">
+        <v>231261.6199556209</v>
+      </c>
+      <c r="E61" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F61" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G61" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H61" s="10">
+        <f>D61+E61+F61+G61-C61</f>
+        <v>-309838.52315581706</v>
+      </c>
+      <c r="I61" s="10">
+        <v>0</v>
+      </c>
+      <c r="J61" s="10">
+        <f>J60+I61-H61</f>
+        <v>1762412.9999887438</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>245</v>
+      </c>
+      <c r="B62" s="10">
+        <v>54</v>
+      </c>
+      <c r="C62" s="10">
+        <v>1196778.883270338</v>
+      </c>
+      <c r="D62" s="10">
+        <v>239355.7766540677</v>
+      </c>
+      <c r="E62" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F62" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G62" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H62" s="10">
+        <f>D62+E62+F62+G62-C62</f>
+        <v>-342215.14994960395</v>
+      </c>
+      <c r="I62" s="10">
+        <v>0</v>
+      </c>
+      <c r="J62" s="10">
+        <f>J61+I62-H62</f>
+        <v>2104628.1499383477</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>246</v>
+      </c>
+      <c r="B63" s="10">
+        <v>55</v>
+      </c>
+      <c r="C63" s="10">
+        <v>1238666.1441848</v>
+      </c>
+      <c r="D63" s="10">
+        <v>247733.22883696</v>
+      </c>
+      <c r="E63" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F63" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G63" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H63" s="10">
+        <f>D63+E63+F63+G63-C63</f>
+        <v>-375724.9586811734</v>
+      </c>
+      <c r="I63" s="10">
+        <v>0</v>
+      </c>
+      <c r="J63" s="10">
+        <f>J62+I63-H63</f>
+        <v>2480353.1086195214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>247</v>
+      </c>
+      <c r="B64" s="10">
+        <v>56</v>
+      </c>
+      <c r="C64" s="10">
+        <v>1282019.459231268</v>
+      </c>
+      <c r="D64" s="10">
+        <v>256403.8918462535</v>
+      </c>
+      <c r="E64" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F64" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G64" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H64" s="10">
+        <f>D64+E64+F64+G64-C64</f>
+        <v>-410407.6107183476</v>
+      </c>
+      <c r="I64" s="10">
+        <v>0</v>
+      </c>
+      <c r="J64" s="10">
+        <f>J63+I64-H64</f>
+        <v>2890760.719337869</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" s="10">
+        <v>57</v>
+      </c>
+      <c r="C65" s="10">
+        <v>1326890.140304362</v>
+      </c>
+      <c r="D65" s="10">
+        <v>265378.0280608724</v>
+      </c>
+      <c r="E65" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F65" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G65" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H65" s="10">
+        <f>D65+E65+F65+G65-C65</f>
+        <v>-446304.15557682305</v>
+      </c>
+      <c r="I65" s="10">
+        <v>0</v>
+      </c>
+      <c r="J65" s="10">
+        <f>J64+I65-H65</f>
+        <v>3337064.874914692</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>249</v>
+      </c>
+      <c r="B66" s="10">
+        <v>58</v>
+      </c>
+      <c r="C66" s="10">
+        <v>1373331.295215015</v>
+      </c>
+      <c r="D66" s="10">
+        <v>274666.2590430029</v>
+      </c>
+      <c r="E66" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F66" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G66" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H66" s="10">
+        <f>D66+E66+F66+G66-C66</f>
+        <v>-483457.0795053451</v>
+      </c>
+      <c r="I66" s="10">
+        <v>0</v>
+      </c>
+      <c r="J66" s="10">
+        <f>J65+I66-H66</f>
+        <v>3820521.9544200366</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>250</v>
+      </c>
+      <c r="B67" s="10">
+        <v>59</v>
+      </c>
+      <c r="C67" s="10">
+        <v>1421397.89054754</v>
+      </c>
+      <c r="D67" s="10">
+        <v>284279.578109508</v>
+      </c>
+      <c r="E67" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F67" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G67" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H67" s="10">
+        <f>D67+E67+F67+G67-C67</f>
+        <v>-521910.35577136546</v>
+      </c>
+      <c r="I67" s="10">
+        <v>0</v>
+      </c>
+      <c r="J67" s="10">
+        <f>J66+I67-H67</f>
+        <v>4342432.310191402</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>251</v>
+      </c>
+      <c r="B68" s="10">
+        <v>60</v>
+      </c>
+      <c r="C68" s="10">
+        <v>1471146.816716704</v>
+      </c>
+      <c r="D68" s="10">
+        <v>294229.3633433408</v>
+      </c>
+      <c r="E68" s="10">
+        <v>394666.6666666666</v>
+      </c>
+      <c r="F68" s="10">
+        <v>80541.29000000001</v>
+      </c>
+      <c r="G68" s="10">
+        <v>140000</v>
+      </c>
+      <c r="H68" s="10">
+        <f>D68+E68+F68+G68-C68</f>
+        <v>-561709.4967066965</v>
+      </c>
+      <c r="I68" s="10">
+        <v>0</v>
+      </c>
+      <c r="J68" s="10">
+        <f>J67+I68-H68</f>
+        <v>4904141.806898098</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="58.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="90.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="10">
+        <f>RAISED_PRESEED_SAFE_USD</f>
+        <v>2000000</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="10">
+        <f>RAISED_SEED_SAFE_USD</f>
+        <v>3500000</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" s="11">
+        <f>B5+B6</f>
+        <v>5500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8" s="10">
+        <f>NET_LOSS_BEFORE_2025_USD</f>
+        <v>592499</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="10">
+        <f>-SUM('P&amp;L'!C27:W27)</f>
+        <v>3107501.24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="11">
+        <f>B7-B8-B9</f>
+        <v>1799999.7599999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="10">
+        <f>CASH_START</f>
+        <v>1800000</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" s="13">
+        <f>B10-B11</f>
+        <v>-0.24000000022351742</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data_room/hollis_voice/02_financials/financial_model.xlsx
+++ b/data_room/hollis_voice/02_financials/financial_model.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Hiring_Plan" sheetId="6" r:id="rId6"/>
     <sheet name="Cash_Runway" sheetId="7" r:id="rId7"/>
     <sheet name="Cash_Bridge" sheetId="8" r:id="rId8"/>
+    <sheet name="Market" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="ARR_TOTAL">ARR_Build!$E$15</definedName>
@@ -29,6 +30,9 @@
     <definedName name="HOSTING_USD_MONTH">Assumptions!$B$13</definedName>
     <definedName name="LICENCES_PCT">Assumptions!$B$12</definedName>
     <definedName name="LOAD_FACTOR">Assumptions!$B$8</definedName>
+    <definedName name="MARKET_ACV_USD">Market!$B$6</definedName>
+    <definedName name="MARKET_CLINICS">Market!$B$5</definedName>
+    <definedName name="MARKET_TAM_USD">Market!$B$7</definedName>
     <definedName name="NET_LOSS_BEFORE_2025_USD">Assumptions!$B$21</definedName>
     <definedName name="NRR_12M">Cohorts!$E$14</definedName>
     <definedName name="PAYROLL_NOW_USD_MONTH">Assumptions!$B$22</definedName>
@@ -49,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="278">
   <si>
     <t>Hollis Voice: financial model</t>
   </si>
@@ -81,6 +85,9 @@
     <t>Cash_Bridge: money raised, less losses since the company began, equals cash at the data date.</t>
   </si>
   <si>
+    <t>Market: the company's own market estimate, the one the deck's market slide uses.</t>
+  </si>
+  <si>
     <t>Definitions</t>
   </si>
   <si>
@@ -621,7 +628,7 @@
     <t>Implementation Specialist</t>
   </si>
   <si>
-    <t>Head of Sales</t>
+    <t>Director of Enterprise Sales</t>
   </si>
   <si>
     <t>Support Specialist</t>
@@ -633,9 +640,6 @@
     <t>Hires in this plan</t>
   </si>
   <si>
-    <t>Staff after these hires</t>
-  </si>
-  <si>
     <t>Cash and runway (USD)</t>
   </si>
   <si>
@@ -856,6 +860,33 @@
   </si>
   <si>
     <t>Rounding only: the loss before 2025 is stated in whole dollars.</t>
+  </si>
+  <si>
+    <t>Market size (USD)</t>
+  </si>
+  <si>
+    <t>These are the company's own estimates. No outside source is in the room.</t>
+  </si>
+  <si>
+    <t>US independent veterinary clinics (company estimate)</t>
+  </si>
+  <si>
+    <t>The same count as the deck's market slide.</t>
+  </si>
+  <si>
+    <t>Annual contract value per clinic (USD, company estimate)</t>
+  </si>
+  <si>
+    <t>A planning figure for what a clinic pays in a year.</t>
+  </si>
+  <si>
+    <t>Market size: clinics times annual contract value (USD)</t>
+  </si>
+  <si>
+    <t>For comparison: subscription ARR per paying clinic today (USD)</t>
+  </si>
+  <si>
+    <t>Subscription ARR in ARR_Build divided by the paying clinics counted there.</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -1322,13 +1353,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="2" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1347,9 +1378,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1369,227 +1405,227 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6">
         <v>1800000</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7">
         <v>0.035</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="6">
         <v>1.28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="6">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="6">
         <v>140000</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="7">
         <v>0.15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="7">
         <v>0.05</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6">
         <v>20541.29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="6">
         <v>60000</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6">
         <v>140000</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6">
         <v>9000000</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6">
         <v>4</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6">
         <v>186739</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="6">
         <v>2000000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="6">
         <v>3500000</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="6">
         <v>592499</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="6">
         <f>STAFF_NOW*AVG_BASE_NOW*LOAD_FACTOR/12</f>
         <v>253866.66666666666</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1609,227 +1645,227 @@
   <sheetData>
     <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:35">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:35">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:35">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:35">
       <c r="A6" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1868,10 +1904,10 @@
     </row>
     <row r="7" spans="1:35">
       <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
         <v>97</v>
-      </c>
-      <c r="B7" t="s">
-        <v>96</v>
       </c>
       <c r="C7" s="10">
         <v>2651</v>
@@ -1939,10 +1975,10 @@
     </row>
     <row r="8" spans="1:35">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -2010,10 +2046,10 @@
     </row>
     <row r="9" spans="1:35">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="10">
         <v>2500</v>
@@ -2117,10 +2153,10 @@
     </row>
     <row r="10" spans="1:35">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" s="10">
         <f>C7+C8</f>
@@ -2245,10 +2281,10 @@
     </row>
     <row r="11" spans="1:35">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="10">
         <f>C10+C9</f>
@@ -2385,7 +2421,7 @@
     </row>
     <row r="12" spans="1:35">
       <c r="A12" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2424,10 +2460,10 @@
     </row>
     <row r="13" spans="1:35">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="10">
         <v>435.7</v>
@@ -2531,10 +2567,10 @@
     </row>
     <row r="14" spans="1:35">
       <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
         <v>105</v>
-      </c>
-      <c r="B14" t="s">
-        <v>104</v>
       </c>
       <c r="C14" s="10">
         <v>148.48</v>
@@ -2638,10 +2674,10 @@
     </row>
     <row r="15" spans="1:35">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="10">
         <f>C13+C14</f>
@@ -2778,7 +2814,7 @@
     </row>
     <row r="16" spans="1:35">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="11">
         <f>C10-C15</f>
@@ -2915,7 +2951,7 @@
     </row>
     <row r="17" spans="1:35">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="12">
         <f>C16/C10</f>
@@ -3052,7 +3088,7 @@
     </row>
     <row r="18" spans="1:35">
       <c r="A18" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -3091,10 +3127,10 @@
     </row>
     <row r="19" spans="1:35">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" s="10">
         <v>31186.59</v>
@@ -3198,10 +3234,10 @@
     </row>
     <row r="20" spans="1:35">
       <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
         <v>112</v>
-      </c>
-      <c r="B20" t="s">
-        <v>111</v>
       </c>
       <c r="C20" s="10">
         <v>384.59</v>
@@ -3305,10 +3341,10 @@
     </row>
     <row r="21" spans="1:35">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="10">
         <v>14987.33</v>
@@ -3412,10 +3448,10 @@
     </row>
     <row r="22" spans="1:35">
       <c r="A22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" t="s">
         <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>114</v>
       </c>
       <c r="C22" s="10">
         <v>0</v>
@@ -3519,10 +3555,10 @@
     </row>
     <row r="23" spans="1:35">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -3626,10 +3662,10 @@
     </row>
     <row r="24" spans="1:35">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" s="10">
         <v>15663.86</v>
@@ -3733,10 +3769,10 @@
     </row>
     <row r="25" spans="1:35">
       <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
         <v>119</v>
-      </c>
-      <c r="B25" t="s">
-        <v>118</v>
       </c>
       <c r="C25" s="10">
         <v>29694.61</v>
@@ -3840,7 +3876,7 @@
     </row>
     <row r="26" spans="1:35">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" s="11">
         <f>C19+C20+C21+C22+C23+C24+C25</f>
@@ -3977,7 +4013,7 @@
     </row>
     <row r="27" spans="1:35">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" s="11">
         <f>C16+C9-C26</f>
@@ -4114,7 +4150,7 @@
     </row>
     <row r="28" spans="1:35">
       <c r="A28" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4153,10 +4189,10 @@
     </row>
     <row r="29" spans="1:35">
       <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
         <v>123</v>
-      </c>
-      <c r="B29" t="s">
-        <v>122</v>
       </c>
       <c r="C29" s="10">
         <f>C19+C21+C22+C24</f>
@@ -4293,10 +4329,10 @@
     </row>
     <row r="30" spans="1:35">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="10">
         <f>-C27</f>
@@ -4433,10 +4469,10 @@
     </row>
     <row r="31" spans="1:35">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C31" s="10">
         <v>4</v>
@@ -4501,46 +4537,10 @@
       <c r="W31" s="10">
         <v>17</v>
       </c>
-      <c r="X31" s="10">
-        <v>19</v>
-      </c>
-      <c r="Y31" s="10">
-        <v>21</v>
-      </c>
-      <c r="Z31" s="10">
-        <v>23</v>
-      </c>
-      <c r="AA31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AB31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AC31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AD31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AE31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AF31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AG31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AH31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AI31" s="10">
-        <v>25</v>
-      </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4561,40 +4561,40 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="10">
         <v>13</v>
@@ -4607,15 +4607,15 @@
         <v>121044</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C6" s="10">
         <v>14</v>
@@ -4628,15 +4628,15 @@
         <v>126420</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="10">
         <v>21</v>
@@ -4649,15 +4649,15 @@
         <v>167820</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="10">
         <v>32</v>
@@ -4670,15 +4670,15 @@
         <v>648864</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="10">
         <v>36</v>
@@ -4691,15 +4691,15 @@
         <v>290532</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="10">
         <v>40</v>
@@ -4712,15 +4712,15 @@
         <v>321060</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="10">
         <v>56</v>
@@ -4733,15 +4733,15 @@
         <v>385128</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(C5:C11)</f>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="10">
         <v>1</v>
@@ -4774,15 +4774,15 @@
         <v>180000</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="10">
         <v>19</v>
@@ -4794,12 +4794,12 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E15" s="6">
         <f>E12+E13+E14</f>
@@ -4808,27 +4808,27 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="10">
         <v>2651</v>
@@ -4843,7 +4843,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="10">
         <v>6828</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="10">
         <v>10024</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="10">
         <v>12366</v>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="10">
         <v>16059</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" s="10">
         <v>19462</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="10">
         <v>23092</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" s="10">
         <v>28610</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="10">
         <v>34539</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="10">
         <v>40585</v>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="10">
         <v>65867</v>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="10">
         <v>72656</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="10">
         <v>77134</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="10">
         <v>85778</v>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="10">
         <v>95824</v>
@@ -5053,7 +5053,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="10">
         <v>122664</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C35" s="10">
         <v>133652</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="10">
         <v>142497</v>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" s="10">
         <v>149831</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="10">
         <v>160971</v>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" s="10">
         <v>171739</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5163,73 +5163,73 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="10">
         <v>4</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="10">
         <v>6</v>
@@ -5343,7 +5343,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="10">
         <v>4</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="10">
         <v>7</v>
@@ -5457,7 +5457,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="10">
         <v>5</v>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10" s="10">
         <v>6</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="10">
         <v>8</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="10">
         <v>8</v>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="10">
         <v>9</v>
@@ -5742,7 +5742,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" s="11">
         <f>SUM(B5:B13)</f>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5783,40 +5783,40 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" s="10">
         <v>191000</v>
@@ -5828,13 +5828,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" s="10">
         <v>139000</v>
@@ -5846,13 +5846,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" s="10">
         <v>189000</v>
@@ -5864,13 +5864,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="10">
         <v>141000</v>
@@ -5882,13 +5882,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="10">
         <v>173500</v>
@@ -5900,13 +5900,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="10">
         <v>156500</v>
@@ -5918,13 +5918,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="10">
         <v>211000</v>
@@ -5936,13 +5936,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" s="10">
         <v>119000</v>
@@ -5954,25 +5954,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" s="6">
         <f>COUNTA(A5:A12)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" s="10">
-        <f>STAFF_NOW+B13</f>
-        <v>25</v>
-      </c>
-    </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6014,7 +6005,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6">
         <f>CASH_START</f>
@@ -6023,7 +6014,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>198</v>
@@ -6032,16 +6023,16 @@
         <v>199</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>200</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>201</v>
@@ -6055,7 +6046,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="10">
         <v>0</v>
@@ -6067,7 +6058,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="10">
         <v>1</v>
@@ -6101,7 +6092,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="10">
         <v>2</v>
@@ -6135,7 +6126,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="10">
         <v>3</v>
@@ -6169,7 +6160,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" s="10">
         <v>4</v>
@@ -6203,7 +6194,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" s="10">
         <v>5</v>
@@ -6237,7 +6228,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="10">
         <v>6</v>
@@ -6271,7 +6262,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="10">
         <v>7</v>
@@ -6305,7 +6296,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="10">
         <v>8</v>
@@ -6339,7 +6330,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="10">
         <v>9</v>
@@ -6373,7 +6364,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18" s="10">
         <v>10</v>
@@ -6407,7 +6398,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B19" s="10">
         <v>11</v>
@@ -6441,7 +6432,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" s="10">
         <v>12</v>
@@ -8107,7 +8098,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -8137,13 +8128,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>254</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8238,7 +8229,91 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="90.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="6">
+        <v>28000</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="6">
+        <v>9000</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="6">
+        <f>MARKET_CLINICS*MARKET_ACV_USD</f>
+        <v>252000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="10">
+        <f>ARR_Build!E12/ARR_Build!C12</f>
+        <v>9721.075471698114</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
